--- a/AMR's Note v2.0.0.xlsx
+++ b/AMR's Note v2.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Programing\-my projects-\chatTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103A99FC-DF8C-40BB-AFCE-33A56D3F1918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C81ABD-86AB-46BB-975C-DB5059376B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main replies" sheetId="1" state="hidden" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="1007">
   <si>
     <t>انا موجود هنا عشان اساعد حضرتك اتفضل اقدر اساعدك ازاي ؟</t>
   </si>
@@ -4250,27 +4250,6 @@
     <t xml:space="preserve">صباح الخير"" مع حضرتك "عمرو" من أورنچ شات , استفسار حضرتك على نفس الرقم ولا رقم تاني؟ , لو رقم تاني وضحه </t>
   </si>
   <si>
-    <t>Orange</t>
-  </si>
-  <si>
-    <t>جالك 5 جيجا هدية شحنة كارت الكبير من اورنچ كاش! ادخل على https://myo.orange.eg/ramadan2026 واختار مجموعتك و كلمهم ببلااااش طول رمضان! القعدة متحلاش غير بـ نت ببلاش!</t>
-  </si>
-  <si>
-    <t>CVM Notifications</t>
-  </si>
-  <si>
-    <t>#012# Recharge Segmented offers</t>
-  </si>
-  <si>
-    <t>MBs</t>
-  </si>
-  <si>
-    <t>IN_PROGRESS</t>
-  </si>
-  <si>
-    <t>CVM redemptions</t>
-  </si>
-  <si>
     <t>AvG</t>
   </si>
   <si>
@@ -4404,6 +4383,217 @@
   </si>
   <si>
     <t>Internet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macro </t>
+  </si>
+  <si>
+    <t>chat-tool99</t>
+  </si>
+  <si>
+    <t>https://chat-tool99.netlify.app/</t>
+  </si>
+  <si>
+    <t>https://github.com/amrkhalid99/chatTool</t>
+  </si>
+  <si>
+    <t>Github</t>
+  </si>
+  <si>
+    <t>\\mob-fs-01\Digital Channels\Click  to chat\Performance\2026</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>C2C</t>
+  </si>
+  <si>
+    <t>Team Member</t>
+  </si>
+  <si>
+    <t>PID</t>
+  </si>
+  <si>
+    <t>Agent Name</t>
+  </si>
+  <si>
+    <t>Customer Segment</t>
+  </si>
+  <si>
+    <t>Agent segment</t>
+  </si>
+  <si>
+    <t>Eval. Status</t>
+  </si>
+  <si>
+    <t>Customer Account</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>FB actor ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post </t>
+  </si>
+  <si>
+    <t>1st Feedback</t>
+  </si>
+  <si>
+    <t>Post Time</t>
+  </si>
+  <si>
+    <t>Feedback Time</t>
+  </si>
+  <si>
+    <t>Non Critical</t>
+  </si>
+  <si>
+    <t>Non-Critical Comments</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>End User Critical</t>
+  </si>
+  <si>
+    <t>Business Critical</t>
+  </si>
+  <si>
+    <t>Compliance critical</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Postpaid Dept. 
+End User Critical</t>
+  </si>
+  <si>
+    <t>Postpaid Dept. 
+Business Critical</t>
+  </si>
+  <si>
+    <t>Postpaid Dept. 
+Grade Critical</t>
+  </si>
+  <si>
+    <t>Critical Comments</t>
+  </si>
+  <si>
+    <t>Responding To customer's Greeting</t>
+  </si>
+  <si>
+    <t>Addressing customer by name</t>
+  </si>
+  <si>
+    <t>Communication Skills</t>
+  </si>
+  <si>
+    <t>Hold</t>
+  </si>
+  <si>
+    <t>Clear Writing</t>
+  </si>
+  <si>
+    <t>Professional Writing</t>
+  </si>
+  <si>
+    <t>Next Step</t>
+  </si>
+  <si>
+    <t>Controlling the call</t>
+  </si>
+  <si>
+    <t>Genesis</t>
+  </si>
+  <si>
+    <t>Applying to internal processes &amp; procedures</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>Penalty</t>
+  </si>
+  <si>
+    <t>SUM Without Bonus</t>
+  </si>
+  <si>
+    <t>SUM With
+Bonus</t>
+  </si>
+  <si>
+    <t>Grade without bonus</t>
+  </si>
+  <si>
+    <t>Grade with bonus</t>
+  </si>
+  <si>
+    <t>Call Info</t>
+  </si>
+  <si>
+    <t>Aggressiveness</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>Problem resolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems tools effectively </t>
+  </si>
+  <si>
+    <t>Business unnecessary call back/cost</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>Samar</t>
+  </si>
+  <si>
+    <t>Whatsapp</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>أتفضل أساعد حضرتك أزاي ؟</t>
+  </si>
+  <si>
+    <t>Amr Khaled Eid Abd Elbaky</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>الخط مش بيستقبل مكالمات</t>
+  </si>
+  <si>
+    <t>ممكن توضيح هل علامة الشبكة ظاهرة على التليفون كاملة؟</t>
+  </si>
+  <si>
+    <t>Home wireless</t>
+  </si>
+  <si>
+    <t>محتاج تجديد الباقع</t>
+  </si>
+  <si>
+    <t>pinned</t>
+  </si>
+  <si>
+    <t>verifcation</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
   <si>
     <t>Sub ExportCleanJson()
@@ -4421,11 +4611,25 @@
         Dim titleVal As String
         Dim catVal As String
         Dim contVal As String
+        Dim pinnedVal As String
         ' بنشيل أي حرف double quote جوه النص عشان يبوظ JSON
         idVal = Replace(ws.Cells(i, 1).Value, """", "\""")
         titleVal = Replace(ws.Cells(i, 2).Value, """", "\""")
         catVal = Replace(ws.Cells(i, 3).Value, """", "\""")
         contVal = Replace(ws.Cells(i, 4).Value, """", "\""")
+        ' الخانة الخامسة (pinned) - بنحولها لقيمة boolean
+        If i &lt;= lastRow And ws.Cells(i, 5).Value &lt;&gt; "" Then
+            ' لو مكتوب TRUE أو YES أو 1 أو أي حاجة إيجابية
+            Dim pinValue As String
+            pinValue = LCase(Trim(ws.Cells(i, 5).Value))
+            If pinValue = "true" Or pinValue = "yes" Or pinValue = "1" Or pinValue = "صح" Or pinValue = "نعم" Then
+                pinnedVal = "true"
+            Else
+                pinnedVal = "false"
+            End If
+        Else
+            pinnedVal = "false"  ' افتراضي false لو الخلية فاضية
+        End If
         ' بنشيل الـ Enter من جوه النص عشان ميقطعش JSON
         contVal = Replace(contVal, vbCrLf, " ")
         contVal = Replace(contVal, vbLf, " ")
@@ -4435,7 +4639,8 @@
         jsonText = jsonText &amp; """id"": """ &amp; idVal &amp; """, "
         jsonText = jsonText &amp; """title"": """ &amp; titleVal &amp; """, "
         jsonText = jsonText &amp; """content"": """ &amp; contVal &amp; """, "
-        jsonText = jsonText &amp; """category"": """ &amp; catVal &amp; """"
+        jsonText = jsonText &amp; """category"": """ &amp; catVal &amp; """, "
+        jsonText = jsonText &amp; """pinned"": " &amp; pinnedVal &amp; ""  ' هنا بدون علامات اقتباس لأنها boolean
         jsonText = jsonText &amp; "}"
         ' لو مش آخر سطر، ضيف فاصلة، مفيش فاصلة بعد آخر سطر
         If i &lt; lastRow Then
@@ -4456,30 +4661,19 @@
 End Sub</t>
   </si>
   <si>
-    <t xml:space="preserve">Macro </t>
-  </si>
-  <si>
-    <t>chat-tool99</t>
-  </si>
-  <si>
-    <t>https://chat-tool99.netlify.app/</t>
-  </si>
-  <si>
-    <t>https://github.com/amrkhalid99/chatTool</t>
-  </si>
-  <si>
-    <t>Github</t>
+    <t>C2c +2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d;@"/>
     <numFmt numFmtId="165" formatCode=";;;"/>
+    <numFmt numFmtId="170" formatCode="[$-409]d\-mmm;@"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="69">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4868,20 +5062,97 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="17"/>
-      <color rgb="FF29303F"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF569CD6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5056,12 +5327,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -5081,6 +5346,54 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7D00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="52"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5685,17 +5998,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -5799,15 +6101,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="275">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6250,18 +6568,6 @@
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="53" fillId="30" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="47" fontId="53" fillId="30" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6284,48 +6590,41 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="28" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6336,19 +6635,20 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6357,10 +6657,10 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6384,6 +6684,18 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6477,18 +6789,6 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6519,15 +6819,140 @@
     <xf numFmtId="0" fontId="30" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="34" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="58" fillId="34" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="62" fillId="37" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="39" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="39" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="40" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="64" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="64" fillId="38" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="36" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="41" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="57" fillId="14" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="57" fillId="14" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="57" fillId="14" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="57" fillId="14" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="57" fillId="14" borderId="27" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="57" fillId="14" borderId="24" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal_Sheet1" xfId="5" xr:uid="{E1DA78A9-11D9-4F15-8691-813EB7C3E466}"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="77">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -6593,6 +7018,43 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -6715,10 +7177,277 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -6734,7 +7463,6 @@
         <sz val="10"/>
         <color theme="0"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -6788,7 +7516,6 @@
         <sz val="14"/>
         <color theme="9"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -6899,13 +7626,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>142876</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>5381987</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>121228</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6943,13 +7670,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>160388</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>71718</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>61246</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7075,13 +7802,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>267123</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>161786</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7119,13 +7846,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3167602</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>95556</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7163,13 +7890,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>367393</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>174387</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7207,13 +7934,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>54429</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>5360980</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>92827</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7251,13 +7978,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>604511</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>181160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7295,13 +8022,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>489857</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>150143</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7339,13 +8066,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>563167</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>76024</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7383,13 +8110,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>26479</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>171262</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8162,11 +8889,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A6:B7" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A6:B7" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75">
   <autoFilter ref="A6:B7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Recharging Fees" dataDxfId="36" dataCellStyle="Neutral"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Main credit" dataDxfId="35">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Recharging Fees" dataDxfId="74" dataCellStyle="Neutral"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Main credit" dataDxfId="73">
       <calculatedColumnFormula>A7*70%</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8175,11 +8902,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A11:B12" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A11:B12" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
   <autoFilter ref="A11:B12" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Main credit" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Recharging Fees" dataDxfId="31" dataCellStyle="Neutral">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Main credit" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Recharging Fees" dataDxfId="69" dataCellStyle="Neutral">
       <calculatedColumnFormula>A12*100/70</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8188,12 +8915,11 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FD0FDEB0-5500-40EF-90D4-5D0A2194DAF6}" name="Table14" displayName="Table14" ref="A1:C1048576" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28">
-  <autoFilter ref="A1:C1048576" xr:uid="{FD0FDEB0-5500-40EF-90D4-5D0A2194DAF6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table14" displayName="Table14" ref="A1:C1048576" totalsRowShown="0" headerRowDxfId="68" headerRowBorderDxfId="67" tableBorderDxfId="66">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D668770A-63CC-435A-9DAC-4A8F95D3A457}" name="id" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{11EC76BC-34B7-426F-861F-D3ABF9A00984}" name="title"/>
-    <tableColumn id="3" xr3:uid="{0B4059AA-5E28-4FD8-8C01-AAEDF14B5433}" name="category" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="id" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="title"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="category" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8562,7 +9288,7 @@
       <c r="A4" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="168" t="s">
+      <c r="B4" s="163" t="s">
         <v>275</v>
       </c>
       <c r="C4" s="136" t="s">
@@ -8582,7 +9308,7 @@
       <c r="A5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="169" t="s">
+      <c r="B5" s="164" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="136" t="s">
@@ -8683,7 +9409,7 @@
         <v>81</v>
       </c>
       <c r="B10" s="134" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="C10" s="136" t="s">
         <v>91</v>
@@ -8711,8 +9437,8 @@
       <c r="D11" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="E11" s="177" t="s">
-        <v>913</v>
+      <c r="E11" s="172" t="s">
+        <v>906</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>819</v>
@@ -8731,8 +9457,8 @@
       <c r="D12" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="E12" s="177" t="s">
-        <v>913</v>
+      <c r="E12" s="172" t="s">
+        <v>906</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>819</v>
@@ -8792,14 +9518,14 @@
         <v>787</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>807</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="25.5">
-      <c r="A16" s="176" t="s">
+      <c r="A16" s="171" t="s">
         <v>40</v>
       </c>
       <c r="B16" s="134" t="s">
@@ -8832,7 +9558,7 @@
         <v>790</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="F17" s="134" t="s">
         <v>4</v>
@@ -8923,12 +9649,12 @@
         <v>271</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:8" ht="30">
-      <c r="A23" s="189" t="s">
+      <c r="A23" s="183" t="s">
         <v>115</v>
       </c>
       <c r="B23" s="134" t="s">
@@ -8943,7 +9669,7 @@
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:8" ht="30">
-      <c r="A24" s="190"/>
+      <c r="A24" s="184"/>
       <c r="B24" s="134" t="s">
         <v>114</v>
       </c>
@@ -8951,7 +9677,7 @@
         <v>21</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -9132,10 +9858,10 @@
       <c r="B37" s="134" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="187" t="s">
+      <c r="C37" s="181" t="s">
         <v>87</v>
       </c>
-      <c r="D37" s="173" t="s">
+      <c r="D37" s="168" t="s">
         <v>88</v>
       </c>
     </row>
@@ -9146,8 +9872,8 @@
       <c r="B38" s="134" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="188"/>
-      <c r="D38" s="175" t="s">
+      <c r="C38" s="182"/>
+      <c r="D38" s="170" t="s">
         <v>89</v>
       </c>
     </row>
@@ -9161,7 +9887,7 @@
       <c r="C39" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="174" t="s">
+      <c r="D39" s="169" t="s">
         <v>18</v>
       </c>
     </row>
@@ -9293,7 +10019,7 @@
         <v>32</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="C49" s="87" t="s">
         <v>265</v>
@@ -9316,8 +10042,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="63.75">
-      <c r="A51" s="171" t="s">
+    <row r="51" spans="1:4" ht="51">
+      <c r="A51" s="166" t="s">
         <v>749</v>
       </c>
       <c r="B51" s="10" t="s">
@@ -9331,7 +10057,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A52" s="171" t="s">
+      <c r="A52" s="166" t="s">
         <v>884</v>
       </c>
       <c r="B52" s="10" t="s">
@@ -9345,7 +10071,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="63.75">
-      <c r="A53" s="191" t="s">
+      <c r="A53" s="185" t="s">
         <v>208</v>
       </c>
       <c r="B53" s="10" t="s">
@@ -9359,7 +10085,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="76.5">
-      <c r="A54" s="192"/>
+      <c r="A54" s="186"/>
       <c r="B54" s="10" t="s">
         <v>834</v>
       </c>
@@ -9371,7 +10097,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="25.5">
-      <c r="A55" s="192"/>
+      <c r="A55" s="186"/>
       <c r="B55" s="10" t="s">
         <v>835</v>
       </c>
@@ -9383,7 +10109,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" ht="89.25">
-      <c r="A56" s="192"/>
+      <c r="A56" s="186"/>
       <c r="B56" s="10" t="s">
         <v>836</v>
       </c>
@@ -9395,7 +10121,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" ht="25.5">
-      <c r="A57" s="192"/>
+      <c r="A57" s="186"/>
       <c r="B57" s="10" t="s">
         <v>18</v>
       </c>
@@ -9407,7 +10133,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="25.5">
-      <c r="A58" s="192"/>
+      <c r="A58" s="186"/>
       <c r="B58" s="10" t="s">
         <v>267</v>
       </c>
@@ -9521,26 +10247,29 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D060D844-4828-4828-99AF-A80D95CD8AD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:AW39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="9.140625" customWidth="1"/>
+    <col min="43" max="45" width="14.5703125" customWidth="1"/>
+    <col min="47" max="47" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="243" t="s">
-        <v>899</v>
-      </c>
-      <c r="B1" s="244"/>
+    <row r="1" spans="1:15">
+      <c r="A1" s="237" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1" s="238"/>
       <c r="C1" s="97" t="s">
         <v>315</v>
       </c>
@@ -9548,31 +10277,32 @@
         <v>282</v>
       </c>
       <c r="E1" s="149" t="s">
-        <v>907</v>
-      </c>
-      <c r="F1" s="181" t="s">
-        <v>921</v>
-      </c>
-      <c r="G1" s="179" t="s">
-        <v>916</v>
-      </c>
-      <c r="H1" s="179" t="s">
-        <v>917</v>
-      </c>
-      <c r="I1" s="179" t="s">
-        <v>918</v>
-      </c>
-      <c r="J1" s="179" t="s">
-        <v>919</v>
-      </c>
-      <c r="K1" s="179" t="s">
-        <v>920</v>
-      </c>
-      <c r="L1" s="149" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>900</v>
+      </c>
+      <c r="F1" s="174" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1" s="149" t="s">
+        <v>900</v>
+      </c>
+      <c r="H1" s="173" t="s">
+        <v>909</v>
+      </c>
+      <c r="I1" s="173" t="s">
+        <v>910</v>
+      </c>
+      <c r="J1" s="173" t="s">
+        <v>911</v>
+      </c>
+      <c r="K1" s="173" t="s">
+        <v>912</v>
+      </c>
+      <c r="L1" s="173" t="s">
+        <v>913</v>
+      </c>
+      <c r="M1" s="240"/>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="98">
         <v>46068</v>
       </c>
@@ -9585,37 +10315,38 @@
       <c r="D2" s="94" t="s">
         <v>768</v>
       </c>
-      <c r="E2" s="178">
-        <f>IF(D2="off",0,1)</f>
+      <c r="E2" s="94" t="str">
+        <f t="shared" ref="E2:E32" si="0">IF(ISNUMBER(D2),"work","non")</f>
+        <v>non</v>
+      </c>
+      <c r="F2" s="175">
+        <f>D33</f>
+        <v>77.666666666666671</v>
+      </c>
+      <c r="G2" s="175">
+        <f>E33</f>
+        <v>6</v>
+      </c>
+      <c r="H2" s="80">
+        <v>2</v>
+      </c>
+      <c r="I2" s="80">
         <v>0</v>
       </c>
-      <c r="F2" s="182">
-        <f>D33</f>
-        <v>75</v>
-      </c>
-      <c r="G2" s="80">
-        <v>2</v>
-      </c>
-      <c r="H2" s="80">
-        <v>0</v>
-      </c>
-      <c r="I2" s="183">
+      <c r="J2" s="176">
         <v>1</v>
       </c>
-      <c r="J2" s="183">
+      <c r="K2" s="176">
         <v>1</v>
       </c>
-      <c r="K2" s="183">
+      <c r="L2" s="176">
         <v>1</v>
       </c>
-      <c r="L2" s="180">
-        <f>E33</f>
-        <v>5</v>
-      </c>
-      <c r="M2" s="150"/>
+      <c r="M2" s="240"/>
       <c r="N2" s="150"/>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" s="150"/>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="98">
         <v>46069</v>
       </c>
@@ -9628,12 +10359,12 @@
       <c r="D3" s="94">
         <v>74</v>
       </c>
-      <c r="E3" s="94">
-        <f t="shared" ref="E3:E10" si="0">IF(D3="off",0,1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="E3" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>work</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="98">
         <v>46070</v>
       </c>
@@ -9646,12 +10377,12 @@
       <c r="D4" s="94" t="s">
         <v>768</v>
       </c>
-      <c r="E4" s="94">
+      <c r="E4" s="94" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>non</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="98">
         <v>46071</v>
       </c>
@@ -9664,12 +10395,12 @@
       <c r="D5" s="94">
         <v>79</v>
       </c>
-      <c r="E5" s="94">
+      <c r="E5" s="94" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>work</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="98">
         <v>46072</v>
       </c>
@@ -9682,12 +10413,12 @@
       <c r="D6" s="94">
         <v>70</v>
       </c>
-      <c r="E6" s="94">
+      <c r="E6" s="94" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>work</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="98">
         <v>46073</v>
       </c>
@@ -9700,12 +10431,12 @@
       <c r="D7" s="94">
         <v>76</v>
       </c>
-      <c r="E7" s="94">
+      <c r="E7" s="94" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>work</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="98">
         <v>46074</v>
       </c>
@@ -9718,12 +10449,12 @@
       <c r="D8" s="94">
         <v>76</v>
       </c>
-      <c r="E8" s="94">
+      <c r="E8" s="94" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>work</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="98">
         <v>46075</v>
       </c>
@@ -9736,12 +10467,12 @@
       <c r="D9" s="94" t="s">
         <v>768</v>
       </c>
-      <c r="E9" s="94">
+      <c r="E9" s="94" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>non</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="98">
         <v>46076</v>
       </c>
@@ -9754,12 +10485,12 @@
       <c r="D10" s="94" t="s">
         <v>768</v>
       </c>
-      <c r="E10" s="94">
+      <c r="E10" s="94" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>non</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="98">
         <v>46077</v>
       </c>
@@ -9769,10 +10500,18 @@
       <c r="C11" s="98">
         <v>46091</v>
       </c>
-      <c r="D11" s="94"/>
-      <c r="E11" s="166"/>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="D11" s="94">
+        <v>91</v>
+      </c>
+      <c r="E11" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>work</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="98">
         <v>46078</v>
       </c>
@@ -9783,9 +10522,12 @@
         <v>46092</v>
       </c>
       <c r="D12" s="94"/>
-      <c r="E12" s="166"/>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="E12" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="98">
         <v>46079</v>
       </c>
@@ -9796,9 +10538,12 @@
         <v>46093</v>
       </c>
       <c r="D13" s="94"/>
-      <c r="E13" s="166"/>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="E13" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="98">
         <v>46080</v>
       </c>
@@ -9809,9 +10554,12 @@
         <v>46094</v>
       </c>
       <c r="D14" s="94"/>
-      <c r="E14" s="166"/>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="E14" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="98">
         <v>46081</v>
       </c>
@@ -9822,13 +10570,16 @@
         <v>46095</v>
       </c>
       <c r="D15" s="94"/>
-      <c r="E15" s="166"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="160" t="s">
-        <v>898</v>
-      </c>
-      <c r="B16" s="161">
+      <c r="E15" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B16" s="157">
         <f>AVERAGE(B2:B15)</f>
         <v>63.7</v>
       </c>
@@ -9836,168 +10587,765 @@
         <v>46096</v>
       </c>
       <c r="D16" s="94"/>
-      <c r="E16" s="166"/>
+      <c r="E16" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" s="98">
         <v>46097</v>
       </c>
       <c r="D17" s="94"/>
-      <c r="E17" s="166"/>
+      <c r="E17" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="18" spans="3:5">
       <c r="C18" s="98">
         <v>46098</v>
       </c>
       <c r="D18" s="94"/>
-      <c r="E18" s="166"/>
+      <c r="E18" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="19" spans="3:5">
       <c r="C19" s="98">
         <v>46099</v>
       </c>
       <c r="D19" s="94"/>
-      <c r="E19" s="166"/>
+      <c r="E19" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="20" spans="3:5">
       <c r="C20" s="98">
         <v>46100</v>
       </c>
       <c r="D20" s="94"/>
-      <c r="E20" s="166"/>
+      <c r="E20" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="21" spans="3:5">
       <c r="C21" s="98">
         <v>46101</v>
       </c>
       <c r="D21" s="94"/>
-      <c r="E21" s="166"/>
+      <c r="E21" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="22" spans="3:5">
       <c r="C22" s="98">
         <v>46102</v>
       </c>
       <c r="D22" s="94"/>
-      <c r="E22" s="166"/>
+      <c r="E22" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="23" spans="3:5">
       <c r="C23" s="98">
         <v>46103</v>
       </c>
       <c r="D23" s="94"/>
-      <c r="E23" s="166"/>
+      <c r="E23" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="24" spans="3:5">
       <c r="C24" s="98">
         <v>46104</v>
       </c>
       <c r="D24" s="94"/>
-      <c r="E24" s="166"/>
+      <c r="E24" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="25" spans="3:5">
       <c r="C25" s="98">
         <v>46105</v>
       </c>
       <c r="D25" s="94"/>
-      <c r="E25" s="166"/>
+      <c r="E25" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="26" spans="3:5">
       <c r="C26" s="98">
         <v>46106</v>
       </c>
       <c r="D26" s="94"/>
-      <c r="E26" s="166"/>
+      <c r="E26" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="27" spans="3:5">
       <c r="C27" s="98">
         <v>46107</v>
       </c>
       <c r="D27" s="94"/>
-      <c r="E27" s="166"/>
+      <c r="E27" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="28" spans="3:5">
       <c r="C28" s="98">
         <v>46108</v>
       </c>
       <c r="D28" s="94"/>
-      <c r="E28" s="166"/>
+      <c r="E28" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="29" spans="3:5">
       <c r="C29" s="98">
         <v>46109</v>
       </c>
       <c r="D29" s="94"/>
-      <c r="E29" s="166"/>
+      <c r="E29" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="30" spans="3:5">
       <c r="C30" s="98">
         <v>46110</v>
       </c>
       <c r="D30" s="94"/>
-      <c r="E30" s="166"/>
+      <c r="E30" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="31" spans="3:5">
       <c r="C31" s="98">
         <v>46111</v>
       </c>
       <c r="D31" s="94"/>
-      <c r="E31" s="166"/>
+      <c r="E31" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
     </row>
     <row r="32" spans="3:5">
       <c r="C32" s="98">
         <v>46112</v>
       </c>
       <c r="D32" s="94"/>
-      <c r="E32" s="166"/>
-    </row>
-    <row r="33" spans="3:5">
-      <c r="C33" s="160" t="s">
-        <v>898</v>
-      </c>
-      <c r="D33" s="161">
+      <c r="E32" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>non</v>
+      </c>
+    </row>
+    <row r="33" spans="1:49">
+      <c r="C33" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="D33" s="157">
         <f>AVERAGE(D2:D32)</f>
-        <v>75</v>
-      </c>
-      <c r="E33" s="161">
-        <f>SUM(E2:E32)</f>
+        <v>77.666666666666671</v>
+      </c>
+      <c r="E33" s="157">
+        <f>COUNTIF(E2:E32,"work")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:49">
+      <c r="E34" s="162" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:49">
+      <c r="AD35" s="273"/>
+      <c r="AE35" s="273"/>
+    </row>
+    <row r="36" spans="1:49" ht="15.75">
+      <c r="A36" s="267" t="s">
+        <v>315</v>
+      </c>
+      <c r="B36" s="267" t="s">
+        <v>944</v>
+      </c>
+      <c r="C36" s="270" t="s">
+        <v>945</v>
+      </c>
+      <c r="D36" s="267" t="s">
+        <v>946</v>
+      </c>
+      <c r="E36" s="271" t="s">
+        <v>947</v>
+      </c>
+      <c r="F36" s="265" t="s">
+        <v>948</v>
+      </c>
+      <c r="G36" s="265" t="s">
+        <v>949</v>
+      </c>
+      <c r="H36" s="267" t="s">
+        <v>950</v>
+      </c>
+      <c r="I36" s="267" t="s">
+        <v>951</v>
+      </c>
+      <c r="J36" s="265" t="s">
+        <v>952</v>
+      </c>
+      <c r="K36" s="265" t="s">
+        <v>953</v>
+      </c>
+      <c r="L36" s="267" t="s">
+        <v>954</v>
+      </c>
+      <c r="M36" s="267" t="s">
+        <v>955</v>
+      </c>
+      <c r="N36" s="267" t="s">
+        <v>956</v>
+      </c>
+      <c r="O36" s="268" t="s">
+        <v>957</v>
+      </c>
+      <c r="P36" s="268"/>
+      <c r="Q36" s="268"/>
+      <c r="R36" s="268"/>
+      <c r="S36" s="268"/>
+      <c r="T36" s="268"/>
+      <c r="U36" s="268"/>
+      <c r="V36" s="268"/>
+      <c r="W36" s="268"/>
+      <c r="X36" s="268"/>
+      <c r="Y36" s="268"/>
+      <c r="Z36" s="268"/>
+      <c r="AA36" s="268"/>
+      <c r="AB36" s="268"/>
+      <c r="AC36" s="268"/>
+      <c r="AD36" s="268"/>
+      <c r="AE36" s="268"/>
+      <c r="AF36" s="239" t="s">
+        <v>958</v>
+      </c>
+      <c r="AG36" s="269" t="s">
+        <v>959</v>
+      </c>
+      <c r="AH36" s="269"/>
+      <c r="AI36" s="269"/>
+      <c r="AJ36" s="269"/>
+      <c r="AK36" s="269"/>
+      <c r="AL36" s="269"/>
+      <c r="AM36" s="269"/>
+      <c r="AN36" s="262" t="s">
+        <v>960</v>
+      </c>
+      <c r="AO36" s="262" t="s">
+        <v>961</v>
+      </c>
+      <c r="AP36" s="263" t="s">
+        <v>962</v>
+      </c>
+      <c r="AQ36" s="264" t="s">
+        <v>963</v>
+      </c>
+      <c r="AR36" s="239" t="s">
+        <v>964</v>
+      </c>
+      <c r="AS36" s="239" t="s">
+        <v>965</v>
+      </c>
+      <c r="AT36" s="263" t="s">
+        <v>962</v>
+      </c>
+      <c r="AU36" s="239" t="s">
+        <v>966</v>
+      </c>
+      <c r="AV36" s="239" t="s">
+        <v>967</v>
+      </c>
+      <c r="AW36" s="241"/>
+    </row>
+    <row r="37" spans="1:49" ht="63.75" customHeight="1">
+      <c r="A37" s="267"/>
+      <c r="B37" s="267"/>
+      <c r="C37" s="270" t="s">
+        <v>950</v>
+      </c>
+      <c r="D37" s="267"/>
+      <c r="E37" s="272"/>
+      <c r="F37" s="266"/>
+      <c r="G37" s="266"/>
+      <c r="H37" s="267" t="s">
+        <v>950</v>
+      </c>
+      <c r="I37" s="267" t="s">
+        <v>950</v>
+      </c>
+      <c r="J37" s="266"/>
+      <c r="K37" s="266"/>
+      <c r="L37" s="267"/>
+      <c r="M37" s="267"/>
+      <c r="N37" s="267"/>
+      <c r="O37" s="242" t="s">
+        <v>968</v>
+      </c>
+      <c r="P37" s="242" t="s">
+        <v>969</v>
+      </c>
+      <c r="Q37" s="242" t="s">
+        <v>970</v>
+      </c>
+      <c r="R37" s="242" t="s">
+        <v>971</v>
+      </c>
+      <c r="S37" s="242" t="s">
+        <v>972</v>
+      </c>
+      <c r="T37" s="242" t="s">
+        <v>973</v>
+      </c>
+      <c r="U37" s="242" t="s">
+        <v>974</v>
+      </c>
+      <c r="V37" s="242" t="s">
+        <v>975</v>
+      </c>
+      <c r="W37" s="242" t="s">
+        <v>976</v>
+      </c>
+      <c r="X37" s="242" t="s">
+        <v>977</v>
+      </c>
+      <c r="Y37" s="242" t="s">
+        <v>978</v>
+      </c>
+      <c r="Z37" s="242" t="s">
+        <v>979</v>
+      </c>
+      <c r="AA37" s="242" t="s">
+        <v>980</v>
+      </c>
+      <c r="AB37" s="243" t="s">
+        <v>981</v>
+      </c>
+      <c r="AC37" s="243" t="s">
+        <v>982</v>
+      </c>
+      <c r="AD37" s="244" t="s">
+        <v>983</v>
+      </c>
+      <c r="AE37" s="244" t="s">
+        <v>984</v>
+      </c>
+      <c r="AF37" s="239"/>
+      <c r="AG37" s="245" t="s">
+        <v>985</v>
+      </c>
+      <c r="AH37" s="245" t="s">
+        <v>986</v>
+      </c>
+      <c r="AI37" s="245" t="s">
+        <v>987</v>
+      </c>
+      <c r="AJ37" s="245" t="s">
+        <v>988</v>
+      </c>
+      <c r="AK37" s="245" t="s">
+        <v>989</v>
+      </c>
+      <c r="AL37" s="246" t="s">
+        <v>990</v>
+      </c>
+      <c r="AM37" s="247" t="s">
+        <v>962</v>
+      </c>
+      <c r="AN37" s="262"/>
+      <c r="AO37" s="262"/>
+      <c r="AP37" s="263"/>
+      <c r="AQ37" s="264"/>
+      <c r="AR37" s="239"/>
+      <c r="AS37" s="239"/>
+      <c r="AT37" s="263"/>
+      <c r="AU37" s="239"/>
+      <c r="AV37" s="239"/>
+      <c r="AW37" s="241" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="38" spans="1:49" ht="120" customHeight="1">
+      <c r="A38" s="248">
+        <v>46083</v>
+      </c>
+      <c r="B38" s="249" t="s">
+        <v>992</v>
+      </c>
+      <c r="C38" s="249">
+        <v>77053</v>
+      </c>
+      <c r="D38" s="249" t="s">
+        <v>996</v>
+      </c>
+      <c r="E38" s="250" t="s">
+        <v>997</v>
+      </c>
+      <c r="F38" s="251" t="s">
+        <v>993</v>
+      </c>
+      <c r="G38" s="251" t="s">
+        <v>994</v>
+      </c>
+      <c r="H38" s="249">
+        <v>1152433540</v>
+      </c>
+      <c r="I38" s="251" t="s">
+        <v>993</v>
+      </c>
+      <c r="J38" s="249">
+        <v>12293174</v>
+      </c>
+      <c r="K38" s="249" t="s">
+        <v>998</v>
+      </c>
+      <c r="L38" s="249" t="s">
+        <v>999</v>
+      </c>
+      <c r="M38" s="248">
+        <v>46081.012557870374</v>
+      </c>
+      <c r="N38" s="248">
+        <v>46081.013206018521</v>
+      </c>
+      <c r="O38" s="252" t="s">
+        <v>216</v>
+      </c>
+      <c r="P38" s="253">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="3:5">
-      <c r="E34" s="167" t="s">
-        <v>908</v>
-      </c>
+      <c r="Q38" s="251">
+        <v>15</v>
+      </c>
+      <c r="R38" s="253" t="s">
+        <v>216</v>
+      </c>
+      <c r="S38" s="253">
+        <v>10</v>
+      </c>
+      <c r="T38" s="253">
+        <v>25</v>
+      </c>
+      <c r="U38" s="253" t="s">
+        <v>216</v>
+      </c>
+      <c r="V38" s="253">
+        <v>10</v>
+      </c>
+      <c r="W38" s="253">
+        <v>5</v>
+      </c>
+      <c r="X38" s="254">
+        <v>20</v>
+      </c>
+      <c r="Y38" s="253" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z38" s="255">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="255">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="256">
+        <v>125</v>
+      </c>
+      <c r="AC38" s="256">
+        <v>125</v>
+      </c>
+      <c r="AD38" s="257">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="257">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="258"/>
+      <c r="AG38" s="259" t="s">
+        <v>216</v>
+      </c>
+      <c r="AH38" s="259" t="s">
+        <v>805</v>
+      </c>
+      <c r="AI38" s="259" t="s">
+        <v>805</v>
+      </c>
+      <c r="AJ38" s="259" t="s">
+        <v>805</v>
+      </c>
+      <c r="AK38" s="259" t="s">
+        <v>216</v>
+      </c>
+      <c r="AL38" s="259" t="s">
+        <v>216</v>
+      </c>
+      <c r="AM38" s="259" t="s">
+        <v>805</v>
+      </c>
+      <c r="AN38" s="260" t="s">
+        <v>805</v>
+      </c>
+      <c r="AO38" s="260" t="s">
+        <v>216</v>
+      </c>
+      <c r="AP38" s="260" t="s">
+        <v>805</v>
+      </c>
+      <c r="AQ38" s="260" t="s">
+        <v>805</v>
+      </c>
+      <c r="AR38" s="261" t="s">
+        <v>805</v>
+      </c>
+      <c r="AS38" s="261" t="s">
+        <v>216</v>
+      </c>
+      <c r="AT38" s="261" t="s">
+        <v>805</v>
+      </c>
+      <c r="AU38" s="261" t="s">
+        <v>805</v>
+      </c>
+      <c r="AV38" s="258"/>
+      <c r="AW38" s="240"/>
+    </row>
+    <row r="39" spans="1:49" ht="120" customHeight="1">
+      <c r="A39" s="248">
+        <v>46083</v>
+      </c>
+      <c r="B39" s="249" t="s">
+        <v>992</v>
+      </c>
+      <c r="C39" s="249">
+        <v>77053</v>
+      </c>
+      <c r="D39" s="249" t="s">
+        <v>996</v>
+      </c>
+      <c r="E39" s="250" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F39" s="251" t="s">
+        <v>993</v>
+      </c>
+      <c r="G39" s="251" t="s">
+        <v>994</v>
+      </c>
+      <c r="H39" s="249">
+        <v>1223651883</v>
+      </c>
+      <c r="I39" s="251" t="s">
+        <v>993</v>
+      </c>
+      <c r="J39" s="249">
+        <v>12291004</v>
+      </c>
+      <c r="K39" s="249" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L39" s="249" t="s">
+        <v>995</v>
+      </c>
+      <c r="M39" s="248">
+        <v>46080.937800925924</v>
+      </c>
+      <c r="N39" s="248">
+        <v>46080.9378125</v>
+      </c>
+      <c r="O39" s="252" t="s">
+        <v>216</v>
+      </c>
+      <c r="P39" s="253">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="251">
+        <v>15</v>
+      </c>
+      <c r="R39" s="253" t="s">
+        <v>216</v>
+      </c>
+      <c r="S39" s="253">
+        <v>10</v>
+      </c>
+      <c r="T39" s="253">
+        <v>25</v>
+      </c>
+      <c r="U39" s="253">
+        <v>10</v>
+      </c>
+      <c r="V39" s="253">
+        <v>10</v>
+      </c>
+      <c r="W39" s="253">
+        <v>5</v>
+      </c>
+      <c r="X39" s="254">
+        <v>20</v>
+      </c>
+      <c r="Y39" s="253" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z39" s="255">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="255">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="256">
+        <v>125</v>
+      </c>
+      <c r="AC39" s="256">
+        <v>125</v>
+      </c>
+      <c r="AD39" s="257">
+        <v>1</v>
+      </c>
+      <c r="AE39" s="257">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="258"/>
+      <c r="AG39" s="259" t="s">
+        <v>805</v>
+      </c>
+      <c r="AH39" s="259" t="s">
+        <v>805</v>
+      </c>
+      <c r="AI39" s="259" t="s">
+        <v>805</v>
+      </c>
+      <c r="AJ39" s="259" t="s">
+        <v>805</v>
+      </c>
+      <c r="AK39" s="259" t="s">
+        <v>216</v>
+      </c>
+      <c r="AL39" s="259" t="s">
+        <v>216</v>
+      </c>
+      <c r="AM39" s="259" t="s">
+        <v>805</v>
+      </c>
+      <c r="AN39" s="260" t="s">
+        <v>805</v>
+      </c>
+      <c r="AO39" s="260" t="s">
+        <v>216</v>
+      </c>
+      <c r="AP39" s="260" t="s">
+        <v>805</v>
+      </c>
+      <c r="AQ39" s="260" t="s">
+        <v>805</v>
+      </c>
+      <c r="AR39" s="261" t="s">
+        <v>805</v>
+      </c>
+      <c r="AS39" s="261" t="s">
+        <v>216</v>
+      </c>
+      <c r="AT39" s="261" t="s">
+        <v>805</v>
+      </c>
+      <c r="AU39" s="261" t="s">
+        <v>805</v>
+      </c>
+      <c r="AV39" s="258"/>
+      <c r="AW39" s="240"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="27">
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="O36:AE36"/>
+    <mergeCell ref="AF36:AF37"/>
+    <mergeCell ref="AG36:AM36"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="AU36:AU37"/>
+    <mergeCell ref="AV36:AV37"/>
+    <mergeCell ref="AO36:AO37"/>
+    <mergeCell ref="AP36:AP37"/>
+    <mergeCell ref="AQ36:AQ37"/>
+    <mergeCell ref="AR36:AR37"/>
+    <mergeCell ref="AS36:AS37"/>
+    <mergeCell ref="AT36:AT37"/>
+    <mergeCell ref="AN36:AN37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="L36:L37"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:B15">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>$C$10=9999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"off"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="11" operator="lessThan">
       <formula>64</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="greaterThan">
       <formula>64</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D32">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$C$10=9999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"off"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="lessThan">
       <formula>64</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>64</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E32">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"work"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"non"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10007,7 +11355,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.140625" customWidth="1"/>
@@ -10016,10 +11364,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="23.25" customHeight="1">
-      <c r="A1" s="194" t="s">
+      <c r="A1" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="194"/>
+      <c r="B1" s="188"/>
       <c r="C1" s="146" t="s">
         <v>837</v>
       </c>
@@ -10047,10 +11395,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="23.25">
-      <c r="A4" s="193" t="s">
+      <c r="A4" s="187" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="193"/>
+      <c r="B4" s="187"/>
       <c r="C4" s="150"/>
     </row>
     <row r="5" spans="1:3" ht="134.25" customHeight="1">
@@ -10076,10 +11424,10 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="23.25">
-      <c r="A7" s="193" t="s">
+      <c r="A7" s="187" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="193"/>
+      <c r="B7" s="187"/>
       <c r="C7" s="150"/>
     </row>
     <row r="8" spans="1:3" ht="127.5">
@@ -10094,10 +11442,10 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="23.25">
-      <c r="A9" s="193" t="s">
+      <c r="A9" s="187" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="193"/>
+      <c r="B9" s="187"/>
       <c r="C9" s="150"/>
     </row>
     <row r="10" spans="1:3" ht="344.25">
@@ -10134,10 +11482,10 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="23.25">
-      <c r="A13" s="193" t="s">
+      <c r="A13" s="187" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="193"/>
+      <c r="B13" s="187"/>
       <c r="C13" s="150"/>
     </row>
     <row r="14" spans="1:3" ht="51">
@@ -10163,13 +11511,13 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="23.25">
-      <c r="A16" s="193" t="s">
+      <c r="A16" s="187" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="193"/>
+      <c r="B16" s="187"/>
       <c r="C16" s="150"/>
     </row>
-    <row r="17" spans="1:3" ht="140.25">
+    <row r="17" spans="1:5" ht="140.25">
       <c r="A17" s="11" t="s">
         <v>78</v>
       </c>
@@ -10177,15 +11525,18 @@
         <v>79</v>
       </c>
       <c r="C17" s="150"/>
-    </row>
-    <row r="18" spans="1:3" ht="23.25">
-      <c r="A18" s="195">
+      <c r="E17">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="23.25">
+      <c r="A18" s="189">
         <v>110</v>
       </c>
-      <c r="B18" s="196"/>
+      <c r="B18" s="190"/>
       <c r="C18" s="150"/>
     </row>
-    <row r="19" spans="1:3" ht="76.5">
+    <row r="19" spans="1:5" ht="76.5">
       <c r="A19" s="3" t="s">
         <v>251</v>
       </c>
@@ -10196,7 +11547,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="140.25">
+    <row r="20" spans="1:5" ht="140.25">
       <c r="A20" s="3" t="s">
         <v>253</v>
       </c>
@@ -10207,7 +11558,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="94.5">
+    <row r="21" spans="1:5" ht="94.5">
       <c r="A21" s="3" t="s">
         <v>255</v>
       </c>
@@ -10218,7 +11569,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="81.75">
+    <row r="22" spans="1:5" ht="81.75">
       <c r="A22" s="3" t="s">
         <v>257</v>
       </c>
@@ -10229,7 +11580,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="81.75">
+    <row r="23" spans="1:5" ht="81.75">
       <c r="A23" s="3" t="s">
         <v>259</v>
       </c>
@@ -10240,7 +11591,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="81.75">
+    <row r="24" spans="1:5" ht="81.75">
       <c r="A24" s="3" t="s">
         <v>261</v>
       </c>
@@ -10251,7 +11602,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="120">
+    <row r="25" spans="1:5" ht="120">
       <c r="A25" s="3" t="s">
         <v>263</v>
       </c>
@@ -10262,14 +11613,14 @@
         <v>852</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="23.25">
-      <c r="A26" s="195" t="s">
+    <row r="26" spans="1:5" ht="23.25">
+      <c r="A26" s="189" t="s">
         <v>97</v>
       </c>
-      <c r="B26" s="196"/>
+      <c r="B26" s="190"/>
       <c r="C26" s="150"/>
     </row>
-    <row r="27" spans="1:3" ht="76.5">
+    <row r="27" spans="1:5" ht="76.5">
       <c r="A27" s="3" t="s">
         <v>95</v>
       </c>
@@ -10280,14 +11631,14 @@
         <v>854</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="23.25">
-      <c r="A28" s="193" t="s">
+    <row r="28" spans="1:5" ht="23.25">
+      <c r="A28" s="187" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="193"/>
+      <c r="B28" s="187"/>
       <c r="C28" s="150"/>
     </row>
-    <row r="29" spans="1:3" ht="127.5">
+    <row r="29" spans="1:5" ht="127.5">
       <c r="A29" s="6" t="s">
         <v>117</v>
       </c>
@@ -10296,14 +11647,14 @@
       </c>
       <c r="C29" s="150"/>
     </row>
-    <row r="30" spans="1:3" ht="23.25">
-      <c r="A30" s="193" t="s">
+    <row r="30" spans="1:5" ht="23.25">
+      <c r="A30" s="187" t="s">
         <v>201</v>
       </c>
-      <c r="B30" s="193"/>
+      <c r="B30" s="187"/>
       <c r="C30" s="150"/>
     </row>
-    <row r="31" spans="1:3" ht="89.25">
+    <row r="31" spans="1:5" ht="89.25">
       <c r="A31" s="72" t="s">
         <v>197</v>
       </c>
@@ -10314,7 +11665,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="76.5">
+    <row r="32" spans="1:5" ht="76.5">
       <c r="A32" s="3" t="s">
         <v>199</v>
       </c>
@@ -10359,10 +11710,10 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="23.25">
-      <c r="A36" s="193" t="s">
+      <c r="A36" s="187" t="s">
         <v>208</v>
       </c>
-      <c r="B36" s="193"/>
+      <c r="B36" s="187"/>
       <c r="C36" s="150"/>
     </row>
     <row r="37" spans="1:3" ht="51">
@@ -10410,10 +11761,10 @@
       </c>
     </row>
     <row r="41" spans="1:3" ht="23.25">
-      <c r="A41" s="193" t="s">
+      <c r="A41" s="187" t="s">
         <v>224</v>
       </c>
-      <c r="B41" s="193"/>
+      <c r="B41" s="187"/>
       <c r="C41" s="150"/>
     </row>
     <row r="42" spans="1:3" ht="242.25">
@@ -10439,10 +11790,10 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="23.25">
-      <c r="A44" s="193" t="s">
+      <c r="A44" s="187" t="s">
         <v>293</v>
       </c>
-      <c r="B44" s="193"/>
+      <c r="B44" s="187"/>
       <c r="C44" s="150"/>
     </row>
     <row r="45" spans="1:3" ht="38.25">
@@ -10473,10 +11824,10 @@
       <c r="C47" s="150"/>
     </row>
     <row r="48" spans="1:3" ht="23.25">
-      <c r="A48" s="193" t="s">
+      <c r="A48" s="187" t="s">
         <v>305</v>
       </c>
-      <c r="B48" s="193"/>
+      <c r="B48" s="187"/>
       <c r="C48" s="150"/>
     </row>
     <row r="49" spans="1:3" ht="63.75">
@@ -10502,10 +11853,10 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="23.25">
-      <c r="A51" s="193" t="s">
+      <c r="A51" s="187" t="s">
         <v>309</v>
       </c>
-      <c r="B51" s="193"/>
+      <c r="B51" s="187"/>
       <c r="C51" s="150"/>
     </row>
     <row r="52" spans="1:3" ht="242.25">
@@ -10518,10 +11869,10 @@
       <c r="C52" s="150"/>
     </row>
     <row r="53" spans="1:3" ht="23.25">
-      <c r="A53" s="193" t="s">
+      <c r="A53" s="187" t="s">
         <v>745</v>
       </c>
-      <c r="B53" s="193"/>
+      <c r="B53" s="187"/>
       <c r="C53" s="150"/>
     </row>
     <row r="54" spans="1:3" ht="127.5">
@@ -10569,10 +11920,10 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="23.25">
-      <c r="A58" s="193" t="s">
+      <c r="A58" s="187" t="s">
         <v>744</v>
       </c>
-      <c r="B58" s="193"/>
+      <c r="B58" s="187"/>
       <c r="C58" s="150"/>
     </row>
     <row r="59" spans="1:3" ht="102">
@@ -10585,10 +11936,10 @@
       <c r="C59" s="150"/>
     </row>
     <row r="60" spans="1:3" ht="23.25">
-      <c r="A60" s="193" t="s">
+      <c r="A60" s="187" t="s">
         <v>754</v>
       </c>
-      <c r="B60" s="193"/>
+      <c r="B60" s="187"/>
       <c r="C60" s="150"/>
     </row>
     <row r="61" spans="1:3" ht="51.75">
@@ -10601,10 +11952,10 @@
       <c r="C61" s="150"/>
     </row>
     <row r="62" spans="1:3" ht="23.25">
-      <c r="A62" s="193" t="s">
+      <c r="A62" s="187" t="s">
         <v>786</v>
       </c>
-      <c r="B62" s="193"/>
+      <c r="B62" s="187"/>
       <c r="C62" s="150"/>
     </row>
     <row r="63" spans="1:3" ht="102">
@@ -10678,11 +12029,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A41:B41"/>
@@ -10697,6 +12043,11 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A51:B51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -10963,17 +12314,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="197" t="s">
-        <v>901</v>
-      </c>
-      <c r="B1" s="197"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
+      <c r="A1" s="191" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
       <c r="F1" s="147" t="s">
         <v>827</v>
       </c>
-      <c r="G1" s="163" t="s">
+      <c r="G1" s="159" t="s">
         <v>825</v>
       </c>
     </row>
@@ -10985,18 +12336,18 @@
         <v>288</v>
       </c>
       <c r="C2" s="93" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="D2" s="93" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="E2" s="93" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="F2" s="147" t="s">
         <v>805</v>
       </c>
-      <c r="G2" s="164" t="s">
+      <c r="G2" s="180" t="s">
         <v>826</v>
       </c>
     </row>
@@ -11009,20 +12360,20 @@
       </c>
       <c r="C3" s="96">
         <f>A3-B5+A5-C5</f>
-        <v>-11</v>
-      </c>
-      <c r="D3" s="165">
+        <v>-26</v>
+      </c>
+      <c r="D3" s="161">
         <f>B3-B5+A5-C5</f>
-        <v>-1</v>
-      </c>
-      <c r="E3" s="165">
+        <v>-16</v>
+      </c>
+      <c r="E3" s="161">
         <f>95-B5+A5-C5</f>
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F3" s="147" t="s">
         <v>828</v>
       </c>
-      <c r="G3" s="163" t="s">
+      <c r="G3" s="159" t="s">
         <v>829</v>
       </c>
     </row>
@@ -11045,23 +12396,23 @@
       <c r="F4" s="147" t="s">
         <v>805</v>
       </c>
-      <c r="G4" s="163" t="s">
+      <c r="G4" s="159" t="s">
         <v>829</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="94">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B5" s="94">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C5" s="94">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D5" s="94">
-        <f>B5-A5+C5</f>
-        <v>76</v>
+        <f>B5-A5+C5+B6</f>
+        <v>93</v>
       </c>
       <c r="E5" s="143" t="s">
         <v>823</v>
@@ -11069,48 +12420,72 @@
       <c r="F5" s="147" t="s">
         <v>831</v>
       </c>
-      <c r="G5" s="163" t="s">
+      <c r="G5" s="159" t="s">
         <v>829</v>
       </c>
     </row>
     <row r="6" spans="1:7">
+      <c r="A6" s="92" t="s">
+        <v>943</v>
+      </c>
+      <c r="B6" s="80">
+        <v>2</v>
+      </c>
       <c r="C6" s="89"/>
+      <c r="D6" s="150">
+        <v>-2</v>
+      </c>
       <c r="E6" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="F6" s="147" t="s">
         <v>805</v>
       </c>
-      <c r="G6" s="164" t="s">
+      <c r="G6" s="160" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="C7" s="89"/>
-      <c r="F7" s="162" t="s">
-        <v>902</v>
-      </c>
-      <c r="G7" s="163"/>
+      <c r="F7" s="158" t="s">
+        <v>895</v>
+      </c>
+      <c r="G7" s="159"/>
     </row>
     <row r="8" spans="1:7">
       <c r="F8" s="147" t="s">
-        <v>900</v>
-      </c>
-      <c r="G8" s="163" t="s">
+        <v>893</v>
+      </c>
+      <c r="G8" s="159" t="s">
         <v>889</v>
       </c>
     </row>
     <row r="29" spans="11:12">
-      <c r="K29" s="159"/>
-      <c r="L29" s="159"/>
+      <c r="K29" s="155"/>
+      <c r="L29" s="155"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="56" type="noConversion"/>
+  <phoneticPr fontId="55" type="noConversion"/>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="lessThan">
+      <formula>65</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="between">
+      <formula>65</formula>
+      <formula>90</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+      <formula>90</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
   <ignoredErrors>
     <ignoredError sqref="F7" numberStoredAsText="1"/>
   </ignoredErrors>
@@ -11120,7 +12495,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="E1:K224"/>
+  <dimension ref="E1:G178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="40.5703125" customWidth="1"/>
@@ -11131,18 +12506,18 @@
   <sheetData>
     <row r="1" spans="5:6" ht="69" customHeight="1">
       <c r="E1" s="80" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="F1" s="99" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
     </row>
     <row r="2" spans="5:6" ht="39" customHeight="1">
       <c r="E2" s="80" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="F2" s="99" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
     </row>
     <row r="3" spans="5:6" ht="44.25" customHeight="1">
@@ -11154,47 +12529,55 @@
       </c>
     </row>
     <row r="4" spans="5:6" ht="50.25" customHeight="1">
-      <c r="E4" s="85" t="s">
-        <v>290</v>
+      <c r="E4" s="80" t="s">
+        <v>942</v>
       </c>
       <c r="F4" s="99" t="s">
-        <v>289</v>
+        <v>941</v>
       </c>
     </row>
     <row r="5" spans="5:6">
       <c r="E5" s="85" t="s">
+        <v>290</v>
+      </c>
+      <c r="F5" s="99" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="5:6">
+      <c r="E6" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="99" t="s">
+      <c r="F6" s="99" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="5:6" ht="47.25">
-      <c r="E6" s="83" t="s">
+    <row r="7" spans="5:6" ht="47.25">
+      <c r="E7" s="83" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="84" t="s">
+      <c r="F7" s="84" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="5:7">
-      <c r="F24" t="s">
+    <row r="25" spans="5:7">
+      <c r="F25" t="s">
         <v>306</v>
-      </c>
-    </row>
-    <row r="26" spans="5:7">
-      <c r="E26">
-        <v>30405</v>
-      </c>
-      <c r="F26" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="27" spans="5:7">
       <c r="E27">
+        <v>30405</v>
+      </c>
+      <c r="F27" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="28" spans="5:7">
+      <c r="E28">
         <v>1601</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F28" t="s">
         <v>761</v>
       </c>
     </row>
@@ -11208,124 +12591,63 @@
         <v>760</v>
       </c>
     </row>
-    <row r="82" spans="5:5">
-      <c r="E82" t="s">
+    <row r="83" spans="5:5">
+      <c r="E83" t="s">
         <v>760</v>
-      </c>
-    </row>
-    <row r="134" spans="5:6">
-      <c r="E134">
-        <v>10113</v>
-      </c>
-      <c r="F134" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="135" spans="5:6">
       <c r="E135">
+        <v>10113</v>
+      </c>
+      <c r="F135" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="136" spans="5:6">
+      <c r="E136">
         <v>10198</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F136" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="154" spans="5:6">
-      <c r="E154" s="80" t="s">
+    <row r="155" spans="5:6">
+      <c r="E155" s="80" t="s">
         <v>821</v>
       </c>
-      <c r="F154" t="s">
+      <c r="F155" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="155" spans="5:6">
-      <c r="F155" s="145" t="s">
+    <row r="156" spans="5:6">
+      <c r="F156" s="145" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="176" spans="5:6" ht="76.5">
-      <c r="E176" s="127" t="s">
+    <row r="177" spans="5:6" ht="76.5">
+      <c r="E177" s="127" t="s">
         <v>885</v>
       </c>
-      <c r="F176" s="128" t="s">
+      <c r="F177" s="128" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="177" spans="5:6" ht="102">
-      <c r="E177" s="127" t="s">
+    <row r="178" spans="5:6" ht="102">
+      <c r="E178" s="127" t="s">
         <v>887</v>
       </c>
-      <c r="F177" s="128" t="s">
+      <c r="F178" s="128" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="220" spans="6:11" ht="15.75" thickBot="1">
-      <c r="F220" s="153" t="s">
-        <v>891</v>
-      </c>
-      <c r="G220" s="154">
-        <v>46088.999305555553</v>
-      </c>
-      <c r="H220" s="153" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="221" spans="6:11">
-      <c r="F221" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="222" spans="6:11" ht="15.75" thickBot="1">
-      <c r="F222" s="153" t="s">
-        <v>894</v>
-      </c>
-      <c r="G222" s="153">
-        <v>12</v>
-      </c>
-      <c r="H222" s="153" t="s">
-        <v>895</v>
-      </c>
-      <c r="I222" s="153">
-        <v>5000</v>
-      </c>
-      <c r="J222" s="155">
-        <v>46089.083029108799</v>
-      </c>
-      <c r="K222" s="153" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="223" spans="6:11" ht="15.75" thickBot="1">
-      <c r="F223" s="153" t="s">
-        <v>894</v>
-      </c>
-      <c r="G223" s="153">
-        <v>12</v>
-      </c>
-      <c r="H223" s="153" t="s">
-        <v>895</v>
-      </c>
-      <c r="I223" s="153">
-        <v>5000</v>
-      </c>
-      <c r="J223" s="155">
-        <v>46089.083029108799</v>
-      </c>
-      <c r="K223" s="153" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="224" spans="6:11" ht="22.5">
-      <c r="F224" s="156" t="s">
-        <v>897</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="56" type="noConversion"/>
+  <phoneticPr fontId="55" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
     <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
-    <hyperlink ref="F6" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
-    <hyperlink ref="F4" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
@@ -11335,7 +12657,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="1" operator="containsText" id="{BBFE5724-4824-43F1-A50B-A65B19CF1978}">
-            <xm:f>NOT(ISERROR(SEARCH("add *155# upselling category",E176)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH("add *155# upselling category",E177)))</xm:f>
             <xm:f>"add *155# upselling category"</xm:f>
             <x14:dxf>
               <font>
@@ -11345,7 +12667,7 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E176:E177</xm:sqref>
+          <xm:sqref>E177:E178</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -11388,13 +12710,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="44.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="198" t="s">
+      <c r="A2" s="192" t="s">
         <v>213</v>
       </c>
-      <c r="B2" s="198"/>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="199"/>
+      <c r="B2" s="192"/>
+      <c r="C2" s="192"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="193"/>
     </row>
     <row r="3" spans="1:5" ht="45" customHeight="1" thickTop="1" thickBot="1">
       <c r="A3" s="70" t="s">
@@ -11552,7 +12874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E4D11E-FD75-44EF-8BBF-7EBDA716AE2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:F143"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11561,20 +12883,24 @@
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="47.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" thickBot="1">
-      <c r="A1" s="184" t="s">
-        <v>922</v>
-      </c>
-      <c r="B1" s="184" t="s">
-        <v>923</v>
-      </c>
-      <c r="C1" s="185" t="s">
-        <v>925</v>
-      </c>
-      <c r="D1" s="185" t="s">
-        <v>924</v>
+      <c r="A1" s="177" t="s">
+        <v>915</v>
+      </c>
+      <c r="B1" s="177" t="s">
+        <v>916</v>
+      </c>
+      <c r="C1" s="178" t="s">
+        <v>918</v>
+      </c>
+      <c r="D1" s="178" t="s">
+        <v>917</v>
+      </c>
+      <c r="E1" s="178" t="s">
+        <v>1002</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="26.25" thickBot="1">
@@ -11585,16 +12911,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="122" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="D2" s="132" t="s">
         <v>890</v>
       </c>
-      <c r="F2" s="185" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="38.25">
+      <c r="E2" s="274" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="178" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="37.5" customHeight="1">
       <c r="A3" s="150">
         <v>2</v>
       </c>
@@ -11602,13 +12931,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="122" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="D3" s="133" t="s">
         <v>752</v>
       </c>
-      <c r="F3" t="s">
-        <v>943</v>
+      <c r="F3" s="1" t="s">
+        <v>1005</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" thickBot="1">
@@ -11619,9 +12948,9 @@
         <v>2</v>
       </c>
       <c r="C4" s="122" t="s">
-        <v>926</v>
-      </c>
-      <c r="D4" s="168" t="s">
+        <v>919</v>
+      </c>
+      <c r="D4" s="163" t="s">
         <v>275</v>
       </c>
     </row>
@@ -11635,7 +12964,7 @@
       <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="169" t="s">
+      <c r="D5" s="164" t="s">
         <v>10</v>
       </c>
     </row>
@@ -11706,7 +13035,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="134" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -11722,6 +13051,9 @@
       <c r="D11" s="134" t="s">
         <v>5</v>
       </c>
+      <c r="E11" s="274" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="25.5">
       <c r="A12" s="150">
@@ -11750,6 +13082,9 @@
       <c r="D13" s="134" t="s">
         <v>17</v>
       </c>
+      <c r="E13" s="274" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="150">
@@ -11759,7 +13094,7 @@
         <v>33</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D14" s="134" t="s">
         <v>12</v>
@@ -11773,7 +13108,7 @@
         <v>36</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D15" s="134" t="s">
         <v>35</v>
@@ -11783,11 +13118,11 @@
       <c r="A16" s="150">
         <v>15</v>
       </c>
-      <c r="B16" s="176" t="s">
+      <c r="B16" s="171" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D16" s="134" t="s">
         <v>105</v>
@@ -11801,7 +13136,7 @@
         <v>72</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D17" s="134" t="s">
         <v>71</v>
@@ -11815,7 +13150,7 @@
         <v>84</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D18" s="134" t="s">
         <v>106</v>
@@ -11829,7 +13164,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D19" s="134" t="s">
         <v>75</v>
@@ -11843,7 +13178,7 @@
         <v>90</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D20" s="134" t="s">
         <v>12</v>
@@ -11857,7 +13192,7 @@
         <v>112</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D21" s="134" t="s">
         <v>202</v>
@@ -11871,7 +13206,7 @@
         <v>112</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D22" s="134" t="s">
         <v>111</v>
@@ -11881,23 +13216,25 @@
       <c r="A23" s="150">
         <v>22</v>
       </c>
-      <c r="B23" s="158" t="s">
+      <c r="B23" s="154" t="s">
         <v>115</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D23" s="134" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.5">
+    <row r="24" spans="1:4" ht="45">
       <c r="A24" s="150">
         <v>23</v>
       </c>
-      <c r="B24" s="122"/>
+      <c r="B24" s="154" t="s">
+        <v>115</v>
+      </c>
       <c r="C24" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D24" s="134" t="s">
         <v>114</v>
@@ -11911,7 +13248,7 @@
         <v>77</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D25" s="134" t="s">
         <v>764</v>
@@ -11925,7 +13262,7 @@
         <v>110</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D26" s="134" t="s">
         <v>109</v>
@@ -11939,7 +13276,7 @@
         <v>82</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D27" s="134" t="s">
         <v>9</v>
@@ -11953,7 +13290,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D28" s="134" t="s">
         <v>284</v>
@@ -11967,7 +13304,7 @@
         <v>281</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D29" s="134" t="s">
         <v>280</v>
@@ -11981,7 +13318,7 @@
         <v>281</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D30" s="134" t="s">
         <v>283</v>
@@ -11995,7 +13332,7 @@
         <v>311</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D31" s="134" t="s">
         <v>310</v>
@@ -12009,7 +13346,7 @@
         <v>774</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D32" s="134" t="s">
         <v>773</v>
@@ -12021,7 +13358,7 @@
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D33" s="134"/>
     </row>
@@ -12033,7 +13370,7 @@
         <v>218</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D34" s="134" t="s">
         <v>219</v>
@@ -12047,7 +13384,7 @@
         <v>218</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D35" s="134" t="s">
         <v>226</v>
@@ -12061,7 +13398,7 @@
         <v>229</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D36" s="134" t="s">
         <v>227</v>
@@ -12075,7 +13412,7 @@
         <v>270</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D37" s="134" t="s">
         <v>42</v>
@@ -12089,7 +13426,7 @@
         <v>270</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D38" s="134" t="s">
         <v>43</v>
@@ -12103,7 +13440,7 @@
         <v>268</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>269</v>
@@ -12117,7 +13454,7 @@
         <v>241</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>762</v>
@@ -12131,7 +13468,7 @@
         <v>241</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>240</v>
@@ -12145,7 +13482,7 @@
         <v>76</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>266</v>
@@ -12159,7 +13496,7 @@
         <v>39</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>85</v>
@@ -12173,7 +13510,7 @@
         <v>731</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>751</v>
@@ -12218,7 +13555,7 @@
         <v>83</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="51">
@@ -12229,10 +13566,10 @@
         <v>16</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="25.5">
@@ -12243,10 +13580,10 @@
         <v>32</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="63.75">
@@ -12257,7 +13594,7 @@
         <v>809</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>810</v>
@@ -12267,25 +13604,25 @@
       <c r="A51" s="150">
         <v>50</v>
       </c>
-      <c r="B51" s="171" t="s">
+      <c r="B51" s="166" t="s">
         <v>749</v>
       </c>
-      <c r="C51" s="186" t="s">
-        <v>931</v>
+      <c r="C51" s="179" t="s">
+        <v>924</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="25.5">
       <c r="A52" s="150">
         <v>51</v>
       </c>
-      <c r="B52" s="171" t="s">
+      <c r="B52" s="166" t="s">
         <v>884</v>
       </c>
-      <c r="C52" s="186" t="s">
-        <v>931</v>
+      <c r="C52" s="179" t="s">
+        <v>924</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>883</v>
@@ -12295,11 +13632,11 @@
       <c r="A53" s="150">
         <v>52</v>
       </c>
-      <c r="B53" s="170" t="s">
+      <c r="B53" s="165" t="s">
         <v>208</v>
       </c>
-      <c r="C53" s="186" t="s">
-        <v>931</v>
+      <c r="C53" s="179" t="s">
+        <v>924</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>833</v>
@@ -12309,11 +13646,11 @@
       <c r="A54" s="150">
         <v>53</v>
       </c>
-      <c r="B54" s="170" t="s">
+      <c r="B54" s="165" t="s">
         <v>208</v>
       </c>
-      <c r="C54" s="186" t="s">
-        <v>931</v>
+      <c r="C54" s="179" t="s">
+        <v>924</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>834</v>
@@ -12323,11 +13660,11 @@
       <c r="A55" s="150">
         <v>54</v>
       </c>
-      <c r="B55" s="170" t="s">
+      <c r="B55" s="165" t="s">
         <v>208</v>
       </c>
-      <c r="C55" s="186" t="s">
-        <v>931</v>
+      <c r="C55" s="179" t="s">
+        <v>924</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>835</v>
@@ -12337,11 +13674,11 @@
       <c r="A56" s="150">
         <v>55</v>
       </c>
-      <c r="B56" s="170" t="s">
+      <c r="B56" s="165" t="s">
         <v>208</v>
       </c>
-      <c r="C56" s="186" t="s">
-        <v>931</v>
+      <c r="C56" s="179" t="s">
+        <v>924</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>836</v>
@@ -12351,25 +13688,25 @@
       <c r="A57" s="150">
         <v>56</v>
       </c>
-      <c r="B57" s="170" t="s">
+      <c r="B57" s="165" t="s">
         <v>208</v>
       </c>
-      <c r="C57" s="186" t="s">
-        <v>931</v>
+      <c r="C57" s="179" t="s">
+        <v>924</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="150">
         <v>57</v>
       </c>
-      <c r="B58" s="170" t="s">
+      <c r="B58" s="165" t="s">
         <v>208</v>
       </c>
-      <c r="C58" s="186" t="s">
-        <v>931</v>
+      <c r="C58" s="179" t="s">
+        <v>924</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>267</v>
@@ -12382,8 +13719,8 @@
       <c r="B59" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C59" s="186" t="s">
-        <v>933</v>
+      <c r="C59" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>6</v>
@@ -12396,8 +13733,8 @@
       <c r="B60" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C60" s="186" t="s">
-        <v>933</v>
+      <c r="C60" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>277</v>
@@ -12410,8 +13747,8 @@
       <c r="B61" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C61" s="186" t="s">
-        <v>933</v>
+      <c r="C61" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>770</v>
@@ -12424,8 +13761,8 @@
       <c r="B62" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C62" s="186" t="s">
-        <v>933</v>
+      <c r="C62" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>817</v>
@@ -12438,8 +13775,8 @@
       <c r="B63" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="186" t="s">
-        <v>933</v>
+      <c r="C63" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>278</v>
@@ -12452,8 +13789,8 @@
       <c r="B64" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="C64" s="186" t="s">
-        <v>933</v>
+      <c r="C64" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>30</v>
@@ -12466,8 +13803,8 @@
       <c r="B65" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C65" s="186" t="s">
-        <v>933</v>
+      <c r="C65" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>747</v>
@@ -12480,8 +13817,8 @@
       <c r="B66" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C66" s="186" t="s">
-        <v>933</v>
+      <c r="C66" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>285</v>
@@ -12494,8 +13831,8 @@
       <c r="B67" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C67" s="186" t="s">
-        <v>933</v>
+      <c r="C67" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>746</v>
@@ -12508,8 +13845,8 @@
       <c r="B68" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C68" s="186" t="s">
-        <v>933</v>
+      <c r="C68" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>789</v>
@@ -12522,8 +13859,8 @@
       <c r="B69" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C69" s="186" t="s">
-        <v>933</v>
+      <c r="C69" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>795</v>
@@ -12536,11 +13873,11 @@
       <c r="B70" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C70" s="186" t="s">
-        <v>933</v>
+      <c r="C70" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="51">
@@ -12550,8 +13887,8 @@
       <c r="B71" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C71" s="186" t="s">
-        <v>933</v>
+      <c r="C71" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>808</v>
@@ -12564,8 +13901,8 @@
       <c r="B72" s="136" t="s">
         <v>791</v>
       </c>
-      <c r="C72" s="186" t="s">
-        <v>933</v>
+      <c r="C72" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>787</v>
@@ -12578,8 +13915,8 @@
       <c r="B73" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="186" t="s">
-        <v>933</v>
+      <c r="C73" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>793</v>
@@ -12592,8 +13929,8 @@
       <c r="B74" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="C74" s="186" t="s">
-        <v>933</v>
+      <c r="C74" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>790</v>
@@ -12606,8 +13943,8 @@
       <c r="B75" s="136" t="s">
         <v>797</v>
       </c>
-      <c r="C75" s="186" t="s">
-        <v>933</v>
+      <c r="C75" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>796</v>
@@ -12618,8 +13955,8 @@
         <v>75</v>
       </c>
       <c r="B76" s="136"/>
-      <c r="C76" s="186" t="s">
-        <v>933</v>
+      <c r="C76" s="179" t="s">
+        <v>926</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>806</v>
@@ -12632,7 +13969,7 @@
       <c r="B77" s="138" t="s">
         <v>29</v>
       </c>
-      <c r="C77" s="186" t="s">
+      <c r="C77" s="179" t="s">
         <v>21</v>
       </c>
       <c r="D77" s="10" t="s">
@@ -12646,7 +13983,7 @@
       <c r="B78" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="C78" s="186" t="s">
+      <c r="C78" s="179" t="s">
         <v>21</v>
       </c>
       <c r="D78" s="10" t="s">
@@ -12660,11 +13997,11 @@
       <c r="B79" s="138" t="s">
         <v>271</v>
       </c>
-      <c r="C79" s="186" t="s">
+      <c r="C79" s="179" t="s">
         <v>21</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="30">
@@ -12674,7 +14011,7 @@
       <c r="B80" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="C80" s="186" t="s">
+      <c r="C80" s="179" t="s">
         <v>21</v>
       </c>
       <c r="D80" s="10" t="s">
@@ -12688,11 +14025,11 @@
       <c r="B81" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="C81" s="186" t="s">
+      <c r="C81" s="179" t="s">
         <v>21</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="30">
@@ -12702,7 +14039,7 @@
       <c r="B82" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="186" t="s">
+      <c r="C82" s="179" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="10" t="s">
@@ -12716,7 +14053,7 @@
       <c r="B83" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="186" t="s">
+      <c r="C83" s="179" t="s">
         <v>21</v>
       </c>
       <c r="D83" s="10" t="s">
@@ -12730,7 +14067,7 @@
       <c r="B84" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="186" t="s">
+      <c r="C84" s="179" t="s">
         <v>21</v>
       </c>
       <c r="D84" s="10" t="s">
@@ -12744,8 +14081,8 @@
       <c r="B85" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="C85" s="186" t="s">
-        <v>935</v>
+      <c r="C85" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>34</v>
@@ -12758,8 +14095,8 @@
       <c r="B86" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="C86" s="186" t="s">
-        <v>935</v>
+      <c r="C86" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>20</v>
@@ -12772,8 +14109,8 @@
       <c r="B87" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="C87" s="186" t="s">
-        <v>935</v>
+      <c r="C87" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>22</v>
@@ -12786,11 +14123,11 @@
       <c r="B88" s="139" t="s">
         <v>24</v>
       </c>
-      <c r="C88" s="186" t="s">
-        <v>935</v>
+      <c r="C88" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="51">
@@ -12800,11 +14137,11 @@
       <c r="B89" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="C89" s="186" t="s">
-        <v>935</v>
+      <c r="C89" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -12814,8 +14151,8 @@
       <c r="B90" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="186" t="s">
-        <v>935</v>
+      <c r="C90" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>13</v>
@@ -12828,11 +14165,11 @@
       <c r="B91" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="C91" s="186" t="s">
-        <v>935</v>
+      <c r="C91" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="25.5">
@@ -12842,8 +14179,8 @@
       <c r="B92" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="C92" s="186" t="s">
-        <v>935</v>
+      <c r="C92" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>86</v>
@@ -12856,8 +14193,8 @@
       <c r="B93" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="C93" s="186" t="s">
-        <v>935</v>
+      <c r="C93" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>107</v>
@@ -12867,13 +14204,13 @@
       <c r="A94" s="150">
         <v>93</v>
       </c>
-      <c r="B94" s="157" t="s">
+      <c r="B94" s="153" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="186" t="s">
-        <v>935</v>
-      </c>
-      <c r="D94" s="173" t="s">
+      <c r="C94" s="179" t="s">
+        <v>928</v>
+      </c>
+      <c r="D94" s="168" t="s">
         <v>88</v>
       </c>
     </row>
@@ -12881,11 +14218,11 @@
       <c r="A95" s="150">
         <v>94</v>
       </c>
-      <c r="B95" s="172"/>
-      <c r="C95" s="186" t="s">
-        <v>935</v>
-      </c>
-      <c r="D95" s="175" t="s">
+      <c r="B95" s="167"/>
+      <c r="C95" s="179" t="s">
+        <v>928</v>
+      </c>
+      <c r="D95" s="170" t="s">
         <v>89</v>
       </c>
     </row>
@@ -12896,11 +14233,11 @@
       <c r="B96" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="C96" s="186" t="s">
-        <v>935</v>
-      </c>
-      <c r="D96" s="174" t="s">
-        <v>939</v>
+      <c r="C96" s="179" t="s">
+        <v>928</v>
+      </c>
+      <c r="D96" s="169" t="s">
+        <v>932</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="30">
@@ -12910,8 +14247,8 @@
       <c r="B97" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="C97" s="186" t="s">
-        <v>935</v>
+      <c r="C97" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>267</v>
@@ -12922,8 +14259,8 @@
         <v>97</v>
       </c>
       <c r="B98" s="140"/>
-      <c r="C98" s="186" t="s">
-        <v>935</v>
+      <c r="C98" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D98" s="10"/>
     </row>
@@ -12934,8 +14271,8 @@
       <c r="B99" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="C99" s="186" t="s">
-        <v>935</v>
+      <c r="C99" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>314</v>
@@ -12948,8 +14285,8 @@
       <c r="B100" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="C100" s="186" t="s">
-        <v>935</v>
+      <c r="C100" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>300</v>
@@ -12962,8 +14299,8 @@
       <c r="B101" s="142" t="s">
         <v>801</v>
       </c>
-      <c r="C101" s="186" t="s">
-        <v>935</v>
+      <c r="C101" s="179" t="s">
+        <v>928</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>800</v>
@@ -12976,8 +14313,8 @@
       <c r="B102" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="C102" s="186" t="s">
-        <v>940</v>
+      <c r="C102" s="179" t="s">
+        <v>933</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>116</v>
@@ -12990,8 +14327,8 @@
       <c r="B103" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="C103" s="186" t="s">
-        <v>940</v>
+      <c r="C103" s="179" t="s">
+        <v>933</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>802</v>
@@ -13004,8 +14341,8 @@
       <c r="B104" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="C104" s="186" t="s">
-        <v>940</v>
+      <c r="C104" s="179" t="s">
+        <v>933</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>803</v>
@@ -13018,8 +14355,8 @@
       <c r="B105" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="C105" s="186" t="s">
-        <v>940</v>
+      <c r="C105" s="179" t="s">
+        <v>933</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>249</v>
@@ -13032,8 +14369,8 @@
       <c r="B106" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="C106" s="186" t="s">
-        <v>940</v>
+      <c r="C106" s="179" t="s">
+        <v>933</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>250</v>
@@ -13046,11 +14383,11 @@
       <c r="B107" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="C107" s="186" t="s">
-        <v>940</v>
+      <c r="C107" s="179" t="s">
+        <v>933</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="51">
@@ -13060,8 +14397,8 @@
       <c r="B108" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="186" t="s">
-        <v>940</v>
+      <c r="C108" s="179" t="s">
+        <v>933</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>272</v>
@@ -13074,8 +14411,8 @@
       <c r="B109" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="C109" s="186" t="s">
-        <v>940</v>
+      <c r="C109" s="179" t="s">
+        <v>933</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>291</v>
@@ -13088,8 +14425,8 @@
       <c r="B110" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="C110" s="186" t="s">
-        <v>940</v>
+      <c r="C110" s="179" t="s">
+        <v>933</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>788</v>
@@ -13102,8 +14439,8 @@
       <c r="B111" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="C111" s="186" t="s">
-        <v>940</v>
+      <c r="C111" s="179" t="s">
+        <v>933</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>792</v>
@@ -13116,7 +14453,7 @@
       <c r="B112" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C112" s="186" t="s">
+      <c r="C112" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D112" s="10" t="s">
@@ -13130,7 +14467,7 @@
       <c r="B113" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C113" s="186" t="s">
+      <c r="C113" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D113" s="10" t="s">
@@ -13144,7 +14481,7 @@
       <c r="B114" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C114" s="186" t="s">
+      <c r="C114" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D114" s="10" t="s">
@@ -13158,7 +14495,7 @@
       <c r="B115" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C115" s="186" t="s">
+      <c r="C115" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D115" s="10" t="s">
@@ -13172,11 +14509,11 @@
       <c r="B116" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="C116" s="186" t="s">
+      <c r="C116" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="25.5">
@@ -13186,7 +14523,7 @@
       <c r="B117" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C117" s="186" t="s">
+      <c r="C117" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D117" s="10" t="s">
@@ -13200,7 +14537,7 @@
       <c r="B118" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C118" s="186" t="s">
+      <c r="C118" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D118" s="10" t="s">
@@ -13214,7 +14551,7 @@
       <c r="B119" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C119" s="186" t="s">
+      <c r="C119" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D119" s="10" t="s">
@@ -13228,7 +14565,7 @@
       <c r="B120" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C120" s="186" t="s">
+      <c r="C120" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D120" s="10" t="s">
@@ -13242,7 +14579,7 @@
       <c r="B121" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C121" s="186" t="s">
+      <c r="C121" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D121" s="10" t="s">
@@ -13256,7 +14593,7 @@
       <c r="B122" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C122" s="186" t="s">
+      <c r="C122" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D122" s="10" t="s">
@@ -13270,7 +14607,7 @@
       <c r="B123" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C123" s="186" t="s">
+      <c r="C123" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D123" s="10" t="s">
@@ -13284,7 +14621,7 @@
       <c r="B124" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C124" s="186" t="s">
+      <c r="C124" s="179" t="s">
         <v>37</v>
       </c>
       <c r="D124" s="10" t="s">
@@ -13298,8 +14635,8 @@
       <c r="B125" s="141" t="s">
         <v>94</v>
       </c>
-      <c r="C125" s="186" t="s">
-        <v>942</v>
+      <c r="C125" s="179" t="s">
+        <v>935</v>
       </c>
       <c r="D125" s="10" t="s">
         <v>93</v>
@@ -13312,8 +14649,8 @@
       <c r="B126" s="141" t="s">
         <v>72</v>
       </c>
-      <c r="C126" s="186" t="s">
-        <v>942</v>
+      <c r="C126" s="179" t="s">
+        <v>935</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>73</v>
@@ -13326,8 +14663,8 @@
       <c r="B127" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="C127" s="186" t="s">
-        <v>942</v>
+      <c r="C127" s="179" t="s">
+        <v>935</v>
       </c>
       <c r="D127" s="134" t="s">
         <v>813</v>
@@ -13340,8 +14677,8 @@
       <c r="B128" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="C128" s="186" t="s">
-        <v>942</v>
+      <c r="C128" s="179" t="s">
+        <v>935</v>
       </c>
       <c r="D128" s="134" t="s">
         <v>104</v>
@@ -13354,8 +14691,8 @@
       <c r="B129" s="137" t="s">
         <v>69</v>
       </c>
-      <c r="C129" s="186" t="s">
-        <v>942</v>
+      <c r="C129" s="137" t="s">
+        <v>1003</v>
       </c>
       <c r="D129" s="10" t="s">
         <v>274</v>
@@ -13368,8 +14705,8 @@
       <c r="B130" s="137" t="s">
         <v>69</v>
       </c>
-      <c r="C130" s="186" t="s">
-        <v>942</v>
+      <c r="C130" s="137" t="s">
+        <v>1003</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>769</v>
@@ -13382,8 +14719,8 @@
       <c r="B131" s="137" t="s">
         <v>69</v>
       </c>
-      <c r="C131" s="186" t="s">
-        <v>942</v>
+      <c r="C131" s="137" t="s">
+        <v>1003</v>
       </c>
       <c r="D131" s="10" t="s">
         <v>70</v>
@@ -13396,8 +14733,8 @@
       <c r="B132" s="137" t="s">
         <v>69</v>
       </c>
-      <c r="C132" s="186" t="s">
-        <v>942</v>
+      <c r="C132" s="137" t="s">
+        <v>1003</v>
       </c>
       <c r="D132" s="10" t="s">
         <v>279</v>
@@ -13410,8 +14747,8 @@
       <c r="B133" s="137" t="s">
         <v>733</v>
       </c>
-      <c r="C133" s="186" t="s">
-        <v>942</v>
+      <c r="C133" s="137" t="s">
+        <v>1003</v>
       </c>
       <c r="D133" s="10" t="s">
         <v>732</v>
@@ -13421,29 +14758,23 @@
       <c r="A134" s="150">
         <v>133</v>
       </c>
-      <c r="B134" s="177" t="s">
-        <v>913</v>
-      </c>
-      <c r="C134" s="186" t="s">
-        <v>942</v>
+      <c r="B134" s="172" t="s">
+        <v>906</v>
+      </c>
+      <c r="C134" s="179" t="s">
+        <v>1004</v>
       </c>
       <c r="D134" s="10" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="25.5">
-      <c r="A135" s="150">
-        <v>134</v>
-      </c>
-      <c r="B135" s="177" t="s">
-        <v>913</v>
-      </c>
-      <c r="C135" s="186" t="s">
-        <v>942</v>
-      </c>
-      <c r="D135" s="10" t="s">
-        <v>819</v>
-      </c>
+    <row r="135" spans="1:4" s="240" customFormat="1">
+      <c r="A135" s="150"/>
+      <c r="B135" s="172"/>
+      <c r="C135" s="179" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D135" s="10"/>
     </row>
     <row r="136" spans="1:4" ht="25.5">
       <c r="A136" s="150">
@@ -13452,8 +14783,8 @@
       <c r="B136" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C136" s="186" t="s">
-        <v>942</v>
+      <c r="C136" s="179" t="s">
+        <v>1004</v>
       </c>
       <c r="D136" s="10" t="s">
         <v>804</v>
@@ -13466,8 +14797,8 @@
       <c r="B137" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C137" s="186" t="s">
-        <v>942</v>
+      <c r="C137" s="179" t="s">
+        <v>1004</v>
       </c>
       <c r="D137" s="134" t="s">
         <v>23</v>
@@ -13478,10 +14809,10 @@
         <v>137</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>910</v>
-      </c>
-      <c r="C138" s="186" t="s">
-        <v>942</v>
+        <v>903</v>
+      </c>
+      <c r="C138" s="179" t="s">
+        <v>1004</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>807</v>
@@ -13494,8 +14825,8 @@
       <c r="B139" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C139" s="186" t="s">
-        <v>942</v>
+      <c r="C139" s="179" t="s">
+        <v>1004</v>
       </c>
       <c r="D139" s="10" t="s">
         <v>102</v>
@@ -13506,10 +14837,10 @@
         <v>139</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>915</v>
-      </c>
-      <c r="C140" s="186" t="s">
-        <v>942</v>
+        <v>908</v>
+      </c>
+      <c r="C140" s="179" t="s">
+        <v>1004</v>
       </c>
       <c r="D140" s="134" t="s">
         <v>4</v>
@@ -13522,8 +14853,8 @@
       <c r="B141" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="C141" s="186" t="s">
-        <v>942</v>
+      <c r="C141" s="179" t="s">
+        <v>1004</v>
       </c>
       <c r="D141" s="10" t="s">
         <v>804</v>
@@ -13536,8 +14867,8 @@
       <c r="B142" s="13" t="s">
         <v>809</v>
       </c>
-      <c r="C142" s="186" t="s">
-        <v>942</v>
+      <c r="C142" s="179" t="s">
+        <v>1004</v>
       </c>
       <c r="D142" s="10" t="s">
         <v>812</v>
@@ -13550,8 +14881,8 @@
       <c r="B143" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="C143" s="186" t="s">
-        <v>942</v>
+      <c r="C143" s="179" t="s">
+        <v>1004</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>811</v>
@@ -13566,7 +14897,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:I230"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13593,26 +14924,26 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="100"/>
-      <c r="B2" s="202" t="s">
+      <c r="B2" s="200" t="s">
         <v>316</v>
       </c>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="204"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="201"/>
+      <c r="E2" s="201"/>
+      <c r="F2" s="201"/>
+      <c r="G2" s="201"/>
+      <c r="H2" s="202"/>
       <c r="I2" s="100"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="100"/>
-      <c r="B3" s="205"/>
-      <c r="C3" s="206"/>
-      <c r="D3" s="206"/>
-      <c r="E3" s="206"/>
-      <c r="F3" s="206"/>
-      <c r="G3" s="206"/>
-      <c r="H3" s="207"/>
+      <c r="B3" s="203"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="204"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="205"/>
       <c r="I3" s="100"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" thickBot="1">
@@ -13621,25 +14952,25 @@
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="100"/>
-      <c r="D5" s="208" t="s">
+      <c r="D5" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="E5" s="209"/>
-      <c r="F5" s="210"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="208"/>
       <c r="I5" s="100"/>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1">
       <c r="A6" s="100"/>
-      <c r="D6" s="211"/>
-      <c r="E6" s="212"/>
-      <c r="F6" s="213"/>
+      <c r="D6" s="209"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="211"/>
       <c r="I6" s="100"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="100"/>
-      <c r="D7" s="214"/>
-      <c r="E7" s="215"/>
-      <c r="F7" s="216"/>
+      <c r="D7" s="212"/>
+      <c r="E7" s="213"/>
+      <c r="F7" s="214"/>
       <c r="I7" s="100"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" thickBot="1">
@@ -13648,25 +14979,25 @@
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="100"/>
-      <c r="D9" s="217" t="s">
+      <c r="D9" s="215" t="s">
         <v>318</v>
       </c>
-      <c r="E9" s="218"/>
-      <c r="F9" s="219"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="217"/>
       <c r="I9" s="100"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="100"/>
-      <c r="D10" s="220"/>
-      <c r="E10" s="221"/>
-      <c r="F10" s="222"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="220"/>
       <c r="I10" s="100"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" thickBot="1">
       <c r="A11" s="100"/>
-      <c r="D11" s="223"/>
-      <c r="E11" s="224"/>
-      <c r="F11" s="225"/>
+      <c r="D11" s="221"/>
+      <c r="E11" s="222"/>
+      <c r="F11" s="223"/>
       <c r="I11" s="100"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
@@ -13675,11 +15006,11 @@
     </row>
     <row r="13" spans="1:9" ht="35.1" customHeight="1" thickBot="1">
       <c r="A13" s="100"/>
-      <c r="D13" s="226" t="s">
+      <c r="D13" s="224" t="s">
         <v>319</v>
       </c>
-      <c r="E13" s="227"/>
-      <c r="F13" s="228"/>
+      <c r="E13" s="225"/>
+      <c r="F13" s="226"/>
       <c r="I13" s="100"/>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -13691,11 +15022,11 @@
       <c r="D15" s="101" t="s">
         <v>320</v>
       </c>
-      <c r="E15" s="229" t="str">
+      <c r="E15" s="227" t="str">
         <f>VLOOKUP(D13,[1]Sheet2!J:K,2,0)</f>
         <v>https://10.53.215.20/#/login</v>
       </c>
-      <c r="F15" s="230"/>
+      <c r="F15" s="228"/>
       <c r="I15" s="100"/>
     </row>
     <row r="16" spans="1:9" ht="21.95" customHeight="1">
@@ -13741,10 +15072,10 @@
       <c r="C22" s="104" t="s">
         <v>323</v>
       </c>
-      <c r="D22" s="200" t="s">
+      <c r="D22" s="198" t="s">
         <v>324</v>
       </c>
-      <c r="E22" s="201"/>
+      <c r="E22" s="199"/>
       <c r="F22" s="104" t="s">
         <v>321</v>
       </c>
@@ -13758,10 +15089,10 @@
       <c r="C23" s="105" t="s">
         <v>319</v>
       </c>
-      <c r="D23" s="231" t="s">
+      <c r="D23" s="194" t="s">
         <v>325</v>
       </c>
-      <c r="E23" s="232"/>
+      <c r="E23" s="195"/>
       <c r="F23" s="105" t="s">
         <v>326</v>
       </c>
@@ -13775,10 +15106,10 @@
       <c r="C24" s="105" t="s">
         <v>328</v>
       </c>
-      <c r="D24" s="231" t="s">
+      <c r="D24" s="194" t="s">
         <v>329</v>
       </c>
-      <c r="E24" s="232"/>
+      <c r="E24" s="195"/>
       <c r="F24" s="105" t="s">
         <v>330</v>
       </c>
@@ -13792,10 +15123,10 @@
       <c r="C25" s="105" t="s">
         <v>332</v>
       </c>
-      <c r="D25" s="231" t="s">
+      <c r="D25" s="194" t="s">
         <v>333</v>
       </c>
-      <c r="E25" s="232"/>
+      <c r="E25" s="195"/>
       <c r="F25" s="105" t="s">
         <v>334</v>
       </c>
@@ -13809,10 +15140,10 @@
       <c r="C26" s="105" t="s">
         <v>336</v>
       </c>
-      <c r="D26" s="231" t="s">
+      <c r="D26" s="194" t="s">
         <v>337</v>
       </c>
-      <c r="E26" s="232"/>
+      <c r="E26" s="195"/>
       <c r="F26" s="105" t="s">
         <v>334</v>
       </c>
@@ -13826,10 +15157,10 @@
       <c r="C27" s="105" t="s">
         <v>338</v>
       </c>
-      <c r="D27" s="231" t="s">
+      <c r="D27" s="194" t="s">
         <v>339</v>
       </c>
-      <c r="E27" s="232"/>
+      <c r="E27" s="195"/>
       <c r="F27" s="105" t="s">
         <v>340</v>
       </c>
@@ -13843,10 +15174,10 @@
       <c r="C28" s="105" t="s">
         <v>341</v>
       </c>
-      <c r="D28" s="231" t="s">
+      <c r="D28" s="194" t="s">
         <v>342</v>
       </c>
-      <c r="E28" s="232"/>
+      <c r="E28" s="195"/>
       <c r="F28" s="105" t="s">
         <v>343</v>
       </c>
@@ -13860,10 +15191,10 @@
       <c r="C29" s="105" t="s">
         <v>344</v>
       </c>
-      <c r="D29" s="231" t="s">
+      <c r="D29" s="194" t="s">
         <v>345</v>
       </c>
-      <c r="E29" s="232"/>
+      <c r="E29" s="195"/>
       <c r="F29" s="105" t="s">
         <v>343</v>
       </c>
@@ -13877,10 +15208,10 @@
       <c r="C30" s="105" t="s">
         <v>346</v>
       </c>
-      <c r="D30" s="231" t="s">
+      <c r="D30" s="194" t="s">
         <v>347</v>
       </c>
-      <c r="E30" s="232"/>
+      <c r="E30" s="195"/>
       <c r="F30" s="105" t="s">
         <v>340</v>
       </c>
@@ -13894,10 +15225,10 @@
       <c r="C31" s="105" t="s">
         <v>348</v>
       </c>
-      <c r="D31" s="231" t="s">
+      <c r="D31" s="194" t="s">
         <v>349</v>
       </c>
-      <c r="E31" s="232"/>
+      <c r="E31" s="195"/>
       <c r="F31" s="4" t="s">
         <v>350</v>
       </c>
@@ -13911,10 +15242,10 @@
       <c r="C32" s="105" t="s">
         <v>352</v>
       </c>
-      <c r="D32" s="231" t="s">
+      <c r="D32" s="194" t="s">
         <v>353</v>
       </c>
-      <c r="E32" s="232"/>
+      <c r="E32" s="195"/>
       <c r="F32" s="4" t="s">
         <v>354</v>
       </c>
@@ -13928,10 +15259,10 @@
       <c r="C33" s="105" t="s">
         <v>356</v>
       </c>
-      <c r="D33" s="231" t="s">
+      <c r="D33" s="194" t="s">
         <v>357</v>
       </c>
-      <c r="E33" s="232"/>
+      <c r="E33" s="195"/>
       <c r="F33" s="4" t="s">
         <v>358</v>
       </c>
@@ -13945,10 +15276,10 @@
       <c r="C34" s="105" t="s">
         <v>360</v>
       </c>
-      <c r="D34" s="231" t="s">
+      <c r="D34" s="194" t="s">
         <v>361</v>
       </c>
-      <c r="E34" s="232"/>
+      <c r="E34" s="195"/>
       <c r="F34" s="105" t="s">
         <v>343</v>
       </c>
@@ -13962,10 +15293,10 @@
       <c r="C35" s="105" t="s">
         <v>362</v>
       </c>
-      <c r="D35" s="231" t="s">
+      <c r="D35" s="194" t="s">
         <v>363</v>
       </c>
-      <c r="E35" s="232"/>
+      <c r="E35" s="195"/>
       <c r="F35" s="105" t="s">
         <v>364</v>
       </c>
@@ -13979,10 +15310,10 @@
       <c r="C36" s="105" t="s">
         <v>366</v>
       </c>
-      <c r="D36" s="231" t="s">
+      <c r="D36" s="194" t="s">
         <v>367</v>
       </c>
-      <c r="E36" s="232"/>
+      <c r="E36" s="195"/>
       <c r="F36" s="105" t="s">
         <v>368</v>
       </c>
@@ -13996,10 +15327,10 @@
       <c r="C37" s="105" t="s">
         <v>369</v>
       </c>
-      <c r="D37" s="231" t="s">
+      <c r="D37" s="194" t="s">
         <v>370</v>
       </c>
-      <c r="E37" s="232"/>
+      <c r="E37" s="195"/>
       <c r="F37" s="105" t="s">
         <v>371</v>
       </c>
@@ -14013,10 +15344,10 @@
       <c r="C38" s="105" t="s">
         <v>373</v>
       </c>
-      <c r="D38" s="231" t="s">
+      <c r="D38" s="194" t="s">
         <v>374</v>
       </c>
-      <c r="E38" s="232"/>
+      <c r="E38" s="195"/>
       <c r="F38" s="106" t="s">
         <v>375</v>
       </c>
@@ -14030,10 +15361,10 @@
       <c r="C39" s="105" t="s">
         <v>377</v>
       </c>
-      <c r="D39" s="231" t="s">
+      <c r="D39" s="194" t="s">
         <v>378</v>
       </c>
-      <c r="E39" s="232"/>
+      <c r="E39" s="195"/>
       <c r="F39" s="105" t="s">
         <v>326</v>
       </c>
@@ -14047,10 +15378,10 @@
       <c r="C40" s="105" t="s">
         <v>379</v>
       </c>
-      <c r="D40" s="231" t="s">
+      <c r="D40" s="194" t="s">
         <v>380</v>
       </c>
-      <c r="E40" s="232"/>
+      <c r="E40" s="195"/>
       <c r="F40" s="105" t="s">
         <v>381</v>
       </c>
@@ -14064,10 +15395,10 @@
       <c r="C41" s="105" t="s">
         <v>383</v>
       </c>
-      <c r="D41" s="231" t="s">
+      <c r="D41" s="194" t="s">
         <v>384</v>
       </c>
-      <c r="E41" s="232"/>
+      <c r="E41" s="195"/>
       <c r="F41" s="106" t="s">
         <v>340</v>
       </c>
@@ -14081,10 +15412,10 @@
       <c r="C42" s="105" t="s">
         <v>385</v>
       </c>
-      <c r="D42" s="231" t="s">
+      <c r="D42" s="194" t="s">
         <v>386</v>
       </c>
-      <c r="E42" s="232"/>
+      <c r="E42" s="195"/>
       <c r="F42" s="105" t="s">
         <v>343</v>
       </c>
@@ -14098,10 +15429,10 @@
       <c r="C43" s="105" t="s">
         <v>387</v>
       </c>
-      <c r="D43" s="231" t="s">
+      <c r="D43" s="194" t="s">
         <v>388</v>
       </c>
-      <c r="E43" s="232"/>
+      <c r="E43" s="195"/>
       <c r="F43" s="105" t="s">
         <v>340</v>
       </c>
@@ -14115,10 +15446,10 @@
       <c r="C44" s="105" t="s">
         <v>389</v>
       </c>
-      <c r="D44" s="231" t="s">
+      <c r="D44" s="194" t="s">
         <v>390</v>
       </c>
-      <c r="E44" s="232"/>
+      <c r="E44" s="195"/>
       <c r="F44" s="105" t="s">
         <v>326</v>
       </c>
@@ -14132,10 +15463,10 @@
       <c r="C45" s="105" t="s">
         <v>391</v>
       </c>
-      <c r="D45" s="233" t="s">
+      <c r="D45" s="197" t="s">
         <v>392</v>
       </c>
-      <c r="E45" s="233"/>
+      <c r="E45" s="197"/>
       <c r="F45" s="105" t="s">
         <v>343</v>
       </c>
@@ -14149,10 +15480,10 @@
       <c r="C46" s="105" t="s">
         <v>393</v>
       </c>
-      <c r="D46" s="233" t="s">
+      <c r="D46" s="197" t="s">
         <v>394</v>
       </c>
-      <c r="E46" s="233"/>
+      <c r="E46" s="197"/>
       <c r="F46" s="105" t="s">
         <v>343</v>
       </c>
@@ -14166,10 +15497,10 @@
       <c r="C47" s="105" t="s">
         <v>395</v>
       </c>
-      <c r="D47" s="233" t="s">
+      <c r="D47" s="197" t="s">
         <v>396</v>
       </c>
-      <c r="E47" s="233"/>
+      <c r="E47" s="197"/>
       <c r="F47" s="105" t="s">
         <v>343</v>
       </c>
@@ -14183,10 +15514,10 @@
       <c r="C48" s="105" t="s">
         <v>397</v>
       </c>
-      <c r="D48" s="233" t="s">
+      <c r="D48" s="197" t="s">
         <v>398</v>
       </c>
-      <c r="E48" s="233"/>
+      <c r="E48" s="197"/>
       <c r="F48" s="108" t="s">
         <v>399</v>
       </c>
@@ -14200,10 +15531,10 @@
       <c r="C49" s="105" t="s">
         <v>401</v>
       </c>
-      <c r="D49" s="233" t="s">
+      <c r="D49" s="197" t="s">
         <v>402</v>
       </c>
-      <c r="E49" s="233"/>
+      <c r="E49" s="197"/>
       <c r="F49" s="105" t="s">
         <v>403</v>
       </c>
@@ -14217,10 +15548,10 @@
       <c r="C50" s="105" t="s">
         <v>405</v>
       </c>
-      <c r="D50" s="233" t="s">
+      <c r="D50" s="197" t="s">
         <v>406</v>
       </c>
-      <c r="E50" s="233"/>
+      <c r="E50" s="197"/>
       <c r="F50" s="105" t="s">
         <v>403</v>
       </c>
@@ -14234,10 +15565,10 @@
       <c r="C51" s="105" t="s">
         <v>407</v>
       </c>
-      <c r="D51" s="233" t="s">
+      <c r="D51" s="197" t="s">
         <v>408</v>
       </c>
-      <c r="E51" s="233"/>
+      <c r="E51" s="197"/>
       <c r="F51" s="105" t="s">
         <v>403</v>
       </c>
@@ -14251,10 +15582,10 @@
       <c r="C52" s="105" t="s">
         <v>409</v>
       </c>
-      <c r="D52" s="233" t="s">
+      <c r="D52" s="197" t="s">
         <v>329</v>
       </c>
-      <c r="E52" s="233"/>
+      <c r="E52" s="197"/>
       <c r="F52" s="105" t="s">
         <v>330</v>
       </c>
@@ -14268,10 +15599,10 @@
       <c r="C53" s="105" t="s">
         <v>410</v>
       </c>
-      <c r="D53" s="231" t="s">
+      <c r="D53" s="194" t="s">
         <v>411</v>
       </c>
-      <c r="E53" s="232"/>
+      <c r="E53" s="195"/>
       <c r="F53" s="105" t="s">
         <v>412</v>
       </c>
@@ -14285,10 +15616,10 @@
       <c r="C54" s="105" t="s">
         <v>414</v>
       </c>
-      <c r="D54" s="231" t="s">
+      <c r="D54" s="194" t="s">
         <v>415</v>
       </c>
-      <c r="E54" s="232"/>
+      <c r="E54" s="195"/>
       <c r="F54" s="105" t="s">
         <v>343</v>
       </c>
@@ -14302,10 +15633,10 @@
       <c r="C55" s="105" t="s">
         <v>416</v>
       </c>
-      <c r="D55" s="231" t="s">
+      <c r="D55" s="194" t="s">
         <v>417</v>
       </c>
-      <c r="E55" s="232"/>
+      <c r="E55" s="195"/>
       <c r="F55" s="105" t="s">
         <v>340</v>
       </c>
@@ -14327,22 +15658,22 @@
     </row>
     <row r="57" spans="1:9" ht="18.75" customHeight="1">
       <c r="B57" s="112"/>
-      <c r="C57" s="234" t="s">
+      <c r="C57" s="196" t="s">
         <v>418</v>
       </c>
-      <c r="D57" s="234"/>
-      <c r="E57" s="234"/>
-      <c r="F57" s="234"/>
-      <c r="G57" s="234"/>
+      <c r="D57" s="196"/>
+      <c r="E57" s="196"/>
+      <c r="F57" s="196"/>
+      <c r="G57" s="196"/>
       <c r="H57" s="112"/>
     </row>
     <row r="58" spans="1:9" ht="14.25" customHeight="1">
       <c r="B58" s="112"/>
-      <c r="C58" s="234"/>
-      <c r="D58" s="234"/>
-      <c r="E58" s="234"/>
-      <c r="F58" s="234"/>
-      <c r="G58" s="234"/>
+      <c r="C58" s="196"/>
+      <c r="D58" s="196"/>
+      <c r="E58" s="196"/>
+      <c r="F58" s="196"/>
+      <c r="G58" s="196"/>
       <c r="H58" s="112"/>
     </row>
     <row r="59" spans="1:9">
@@ -16351,16 +17682,24 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="C57:G58"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="D5:F7"/>
+    <mergeCell ref="D9:F11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="D36:E36"/>
@@ -16373,51 +17712,43 @@
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="D5:F7"/>
-    <mergeCell ref="D9:F11"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="C57:G58"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:F13" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:F13" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>Tool_Name</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G37" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
-    <hyperlink ref="D31" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
-    <hyperlink ref="D29" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
-    <hyperlink ref="D27" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
-    <hyperlink ref="D38" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
-    <hyperlink ref="D23" r:id="rId6" location="/login" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
-    <hyperlink ref="D47" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
-    <hyperlink ref="D55" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
-    <hyperlink ref="D30" r:id="rId9" location="GENERAL_HomeView" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
-    <hyperlink ref="D39" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
-    <hyperlink ref="G50" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
-    <hyperlink ref="D41" r:id="rId12" xr:uid="{00000000-0004-0000-0600-00000B000000}"/>
-    <hyperlink ref="D24" r:id="rId13" xr:uid="{00000000-0004-0000-0600-00000C000000}"/>
-    <hyperlink ref="D54" r:id="rId14" xr:uid="{00000000-0004-0000-0600-00000D000000}"/>
-    <hyperlink ref="D44" r:id="rId15" xr:uid="{00000000-0004-0000-0600-00000E000000}"/>
-    <hyperlink ref="D52" r:id="rId16" xr:uid="{00000000-0004-0000-0600-00000F000000}"/>
-    <hyperlink ref="D46" r:id="rId17" xr:uid="{00000000-0004-0000-0600-000010000000}"/>
-    <hyperlink ref="D26" r:id="rId18" location="/login" xr:uid="{00000000-0004-0000-0600-000011000000}"/>
-    <hyperlink ref="F48" r:id="rId19" xr:uid="{00000000-0004-0000-0600-000012000000}"/>
-    <hyperlink ref="G48" r:id="rId20" xr:uid="{00000000-0004-0000-0600-000013000000}"/>
+    <hyperlink ref="G37" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+    <hyperlink ref="D31" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
+    <hyperlink ref="D29" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
+    <hyperlink ref="D27" r:id="rId4" xr:uid="{00000000-0004-0000-0700-000003000000}"/>
+    <hyperlink ref="D38" r:id="rId5" xr:uid="{00000000-0004-0000-0700-000004000000}"/>
+    <hyperlink ref="D23" r:id="rId6" location="/login" xr:uid="{00000000-0004-0000-0700-000005000000}"/>
+    <hyperlink ref="D47" r:id="rId7" xr:uid="{00000000-0004-0000-0700-000006000000}"/>
+    <hyperlink ref="D55" r:id="rId8" xr:uid="{00000000-0004-0000-0700-000007000000}"/>
+    <hyperlink ref="D30" r:id="rId9" location="GENERAL_HomeView" xr:uid="{00000000-0004-0000-0700-000008000000}"/>
+    <hyperlink ref="D39" r:id="rId10" xr:uid="{00000000-0004-0000-0700-000009000000}"/>
+    <hyperlink ref="G50" r:id="rId11" xr:uid="{00000000-0004-0000-0700-00000A000000}"/>
+    <hyperlink ref="D41" r:id="rId12" xr:uid="{00000000-0004-0000-0700-00000B000000}"/>
+    <hyperlink ref="D24" r:id="rId13" xr:uid="{00000000-0004-0000-0700-00000C000000}"/>
+    <hyperlink ref="D54" r:id="rId14" xr:uid="{00000000-0004-0000-0700-00000D000000}"/>
+    <hyperlink ref="D44" r:id="rId15" xr:uid="{00000000-0004-0000-0700-00000E000000}"/>
+    <hyperlink ref="D52" r:id="rId16" xr:uid="{00000000-0004-0000-0700-00000F000000}"/>
+    <hyperlink ref="D46" r:id="rId17" xr:uid="{00000000-0004-0000-0700-000010000000}"/>
+    <hyperlink ref="D26" r:id="rId18" location="/login" xr:uid="{00000000-0004-0000-0700-000011000000}"/>
+    <hyperlink ref="F48" r:id="rId19" xr:uid="{00000000-0004-0000-0700-000012000000}"/>
+    <hyperlink ref="G48" r:id="rId20" xr:uid="{00000000-0004-0000-0700-000013000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId21"/>
@@ -16425,7 +17756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16439,21 +17770,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21">
-      <c r="A1" s="235" t="s">
+      <c r="A1" s="229" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="237" t="s">
+      <c r="B1" s="231" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="237"/>
+      <c r="C1" s="231"/>
       <c r="D1" s="14"/>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="231" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="238"/>
+      <c r="F1" s="232"/>
     </row>
     <row r="2" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A2" s="236"/>
+      <c r="A2" s="230"/>
       <c r="B2" s="15" t="s">
         <v>123</v>
       </c>
@@ -16613,7 +17944,7 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="239" t="s">
+      <c r="A11" s="233" t="s">
         <v>165</v>
       </c>
       <c r="B11" s="38"/>
@@ -16623,7 +17954,7 @@
       <c r="F11" s="42"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="240"/>
+      <c r="A12" s="234"/>
       <c r="B12" s="43"/>
       <c r="C12" s="44"/>
       <c r="D12" s="45"/>
@@ -16635,7 +17966,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="38.25">
-      <c r="A13" s="240"/>
+      <c r="A13" s="234"/>
       <c r="B13" s="43"/>
       <c r="C13" s="27" t="s">
         <v>168</v>
@@ -16647,7 +17978,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="38.25">
-      <c r="A14" s="240"/>
+      <c r="A14" s="234"/>
       <c r="B14" s="47"/>
       <c r="C14" s="27" t="s">
         <v>170</v>
@@ -16659,7 +17990,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="25.5">
-      <c r="A15" s="240"/>
+      <c r="A15" s="234"/>
       <c r="B15" s="43"/>
       <c r="C15" s="27"/>
       <c r="D15" s="28"/>
@@ -16669,7 +18000,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="25.5">
-      <c r="A16" s="240"/>
+      <c r="A16" s="234"/>
       <c r="B16" s="43"/>
       <c r="C16" s="27"/>
       <c r="D16" s="28"/>
@@ -16679,7 +18010,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="25.5">
-      <c r="A17" s="240"/>
+      <c r="A17" s="234"/>
       <c r="B17" s="43"/>
       <c r="C17" s="27"/>
       <c r="D17" s="28"/>
@@ -16689,7 +18020,7 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="240"/>
+      <c r="A18" s="234"/>
       <c r="B18" s="47"/>
       <c r="C18" s="48" t="s">
         <v>175</v>
@@ -16701,7 +18032,7 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="241"/>
+      <c r="A19" s="235"/>
       <c r="B19" s="50"/>
       <c r="C19" s="34"/>
       <c r="D19" s="35"/>
@@ -16711,7 +18042,7 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="241"/>
+      <c r="A20" s="235"/>
       <c r="B20" s="50"/>
       <c r="C20" s="34"/>
       <c r="D20" s="35"/>
@@ -16721,7 +18052,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="26.25" thickBot="1">
-      <c r="A21" s="242"/>
+      <c r="A21" s="236"/>
       <c r="B21" s="53"/>
       <c r="C21" s="54" t="s">
         <v>179</v>

--- a/AMR's Note v2.0.0.xlsx
+++ b/AMR's Note v2.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Programing\-my projects-\chatTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C32DD91-14CF-4121-8E1D-0C19841CAE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C81B8FB-5B4F-44E7-A5EE-42E962389B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main replies" sheetId="1" state="hidden" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Say &amp; Dont Say " sheetId="4" state="hidden" r:id="rId9"/>
     <sheet name="Perfomance" sheetId="13" r:id="rId10"/>
     <sheet name="March" sheetId="16" state="hidden" r:id="rId11"/>
-    <sheet name="FEB" sheetId="15" r:id="rId12"/>
+    <sheet name="FEB" sheetId="15" state="hidden" r:id="rId12"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId13"/>
